--- a/docs/일반조서/일반조서_조서별규칙_초안.xlsx
+++ b/docs/일반조서/일반조서_조서별규칙_초안.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\geniw\JAYTAX개발\docs\일반조서\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65129136-21BB-4C34-B4BA-7D42B251AFD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37105A1C-B419-43CB-883D-A5DD84294161}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12375" yWindow="2025" windowWidth="15330" windowHeight="10770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="조서별 규칙" sheetId="1" r:id="rId1"/>
@@ -18,9 +18,9 @@
     <sheet name="요약" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'조서별 규칙'!$A$1:$K$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'조서별 규칙'!$A$1:$L$72</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="356">
   <si>
     <t>섹션</t>
   </si>
@@ -73,6 +73,9 @@
     <t>수정의견 ✏️</t>
   </si>
   <si>
+    <t>반영 내역(09-26)</t>
+  </si>
+  <si>
     <t>공통</t>
   </si>
   <si>
@@ -136,168 +139,195 @@
     <t>계획</t>
   </si>
   <si>
+    <t>ERP 에서 평가를 마친 조서 — 본문에 「ERP 에서 수행함」으로 적는다</t>
+  </si>
+  <si>
+    <t>ERP 수행 문구를 넣고 그대로</t>
+  </si>
+  <si>
+    <t>머리 2025-04-14 · 값 26칸</t>
+  </si>
+  <si>
+    <t>erp평가를 마친 상태이며 erp에서 기재했다고 적어야 함. 즉 해당 일반조서작성은 erp 환경에서 기수행됨.</t>
+  </si>
+  <si>
+    <t>✓ 수정의견: ERP 에서 기수행</t>
+  </si>
+  <si>
+    <t>1100A</t>
+  </si>
+  <si>
+    <t>계약전 위험평가표(수임)</t>
+  </si>
+  <si>
+    <t>조건부</t>
+  </si>
+  <si>
+    <t>신규 수임(초도)일 때 · ERP 에서 평가를 마친 조서 — 본문에 「ERP 에서 수행함」으로 적는다</t>
+  </si>
+  <si>
+    <t>숨김 · 값 805칸</t>
+  </si>
+  <si>
+    <t>1200</t>
+  </si>
+  <si>
+    <t>독립성, 윤리규정 및 품질관리기준의 준수</t>
+  </si>
+  <si>
+    <t>머리 2025-04-14 · 값 9칸</t>
+  </si>
+  <si>
+    <t>1300C</t>
+  </si>
+  <si>
+    <t>산업전문가 검토</t>
+  </si>
+  <si>
+    <t>K-IFRS 적용기업에만</t>
+  </si>
+  <si>
+    <t>명진에 없음</t>
+  </si>
+  <si>
+    <t>산업전문가는 K-IFRS 적용기업에만 해당함</t>
+  </si>
+  <si>
+    <t>✓ 수정의견: K-IFRS 에만</t>
+  </si>
+  <si>
+    <t>2000 위험평가</t>
+  </si>
+  <si>
+    <t>2100</t>
+  </si>
+  <si>
+    <t>기업과 기업 환경에 대한 이해</t>
+  </si>
+  <si>
+    <t>④</t>
+  </si>
+  <si>
+    <t>★ 초안 도움 대상 — 전기 내용 + 거래처 정보</t>
+  </si>
+  <si>
+    <t>전기 내용 보존 · 당기를 덧붙일 자리 표시</t>
+  </si>
+  <si>
+    <t>머리 2025-04-14 · 값 28칸</t>
+  </si>
+  <si>
+    <t>중간</t>
+  </si>
+  <si>
+    <t>2100A</t>
+  </si>
+  <si>
+    <t>회사의 사업 및 법규에 대한 이해요약표</t>
+  </si>
+  <si>
+    <t>★ 초안 도움 대상</t>
+  </si>
+  <si>
+    <t>값 197칸(서술)</t>
+  </si>
+  <si>
+    <t>2110</t>
+  </si>
+  <si>
+    <t>감사계획의 수립</t>
+  </si>
+  <si>
     <t>②</t>
   </si>
   <si>
-    <t>계약조건·보수가 바뀌면 그 칸</t>
+    <t>일정·투입인력·감사팀 구성</t>
   </si>
   <si>
     <t>이월본 + 본문의 날짜·담당자 칸을 확인 목록으로</t>
   </si>
   <si>
-    <t>머리 2025-04-14 · 값 26칸</t>
-  </si>
-  <si>
-    <t>1100A</t>
-  </si>
-  <si>
-    <t>계약전 위험평가표(수임)</t>
+    <t>값 39칸</t>
+  </si>
+  <si>
+    <t>2110-1</t>
+  </si>
+  <si>
+    <t>감사전략계획서(ASM)</t>
+  </si>
+  <si>
+    <t>별도 파일(docx) — Audit Lobby 에 따로 올림</t>
+  </si>
+  <si>
+    <t>AuditLobby 폴더에 docx</t>
+  </si>
+  <si>
+    <t>2110-2</t>
+  </si>
+  <si>
+    <t>계약후 감사위험 재평가</t>
+  </si>
+  <si>
+    <t>특이사항이 없으면 그대로 · 예외: 초도, 전기 감사인 변경</t>
+  </si>
+  <si>
+    <t>값 75칸</t>
+  </si>
+  <si>
+    <t>답이 거의 매년 같음. 즉 특이사항 발생하지 않는한 동의함(초도 전기외감인 회사 정도?)</t>
+  </si>
+  <si>
+    <t>✓ 수정의견: 매년 같음 동의</t>
+  </si>
+  <si>
+    <t>2110A</t>
+  </si>
+  <si>
+    <t>업무분장표</t>
+  </si>
+  <si>
+    <t>감사팀 구성·담당</t>
+  </si>
+  <si>
+    <t>값 182칸</t>
+  </si>
+  <si>
+    <t>2120</t>
+  </si>
+  <si>
+    <t>분석적절차(계획단계)</t>
+  </si>
+  <si>
+    <t>결론 문장 — 2120A 를 링크로 건다</t>
+  </si>
+  <si>
+    <t>2120A 링크를 걸고 날짜·담당자 확인</t>
+  </si>
+  <si>
+    <t>값 6칸</t>
+  </si>
+  <si>
+    <t>[2120A]조서를 링크로 걸어야함</t>
+  </si>
+  <si>
+    <t>✓ 수정의견: 2120A 링크</t>
+  </si>
+  <si>
+    <t>2120A</t>
+  </si>
+  <si>
+    <t>계획단계 분석적검토</t>
   </si>
   <si>
     <t>③</t>
   </si>
   <si>
-    <t>조건부</t>
-  </si>
-  <si>
-    <t>신규 수임(초도)일 때</t>
+    <t>당기 가결산 숫자 · 2차 화면 입력 후보</t>
   </si>
   <si>
     <t>전기를 틀로 두고 「당기 작성」 표시</t>
   </si>
   <si>
-    <t>숨김 · 값 805칸</t>
-  </si>
-  <si>
-    <t>중간</t>
-  </si>
-  <si>
-    <t>1200</t>
-  </si>
-  <si>
-    <t>독립성, 윤리규정 및 품질관리기준의 준수</t>
-  </si>
-  <si>
-    <t>머리 2025-04-14 · 값 9칸</t>
-  </si>
-  <si>
-    <t>1300C</t>
-  </si>
-  <si>
-    <t>산업전문가 검토</t>
-  </si>
-  <si>
-    <t>K-IFRS 묶음에만 있음</t>
-  </si>
-  <si>
-    <t>명진에 없음</t>
-  </si>
-  <si>
-    <t>낮음</t>
-  </si>
-  <si>
-    <t>2000 위험평가</t>
-  </si>
-  <si>
-    <t>2100</t>
-  </si>
-  <si>
-    <t>기업과 기업 환경에 대한 이해</t>
-  </si>
-  <si>
-    <t>④</t>
-  </si>
-  <si>
-    <t>★ 초안 도움 대상 — 전기 내용 + 거래처 정보</t>
-  </si>
-  <si>
-    <t>전기 내용 보존 · 당기를 덧붙일 자리 표시</t>
-  </si>
-  <si>
-    <t>머리 2025-04-14 · 값 28칸</t>
-  </si>
-  <si>
-    <t>2100A</t>
-  </si>
-  <si>
-    <t>회사의 사업 및 법규에 대한 이해요약표</t>
-  </si>
-  <si>
-    <t>★ 초안 도움 대상</t>
-  </si>
-  <si>
-    <t>값 197칸(서술)</t>
-  </si>
-  <si>
-    <t>2110</t>
-  </si>
-  <si>
-    <t>감사계획의 수립</t>
-  </si>
-  <si>
-    <t>일정·투입인력·감사팀 구성</t>
-  </si>
-  <si>
-    <t>값 39칸</t>
-  </si>
-  <si>
-    <t>2110-1</t>
-  </si>
-  <si>
-    <t>감사전략계획서(ASM)</t>
-  </si>
-  <si>
-    <t>별도 파일(docx) — Audit Lobby 에 따로 올림</t>
-  </si>
-  <si>
-    <t>AuditLobby 폴더에 docx</t>
-  </si>
-  <si>
-    <t>2110-2</t>
-  </si>
-  <si>
-    <t>계약후 감사위험 재평가</t>
-  </si>
-  <si>
-    <t>체크리스트 — 답이 매년 거의 같음</t>
-  </si>
-  <si>
-    <t>값 75칸</t>
-  </si>
-  <si>
-    <t>2110A</t>
-  </si>
-  <si>
-    <t>업무분장표</t>
-  </si>
-  <si>
-    <t>감사팀 구성·담당</t>
-  </si>
-  <si>
-    <t>값 182칸</t>
-  </si>
-  <si>
-    <t>2120</t>
-  </si>
-  <si>
-    <t>분석적절차(계획단계)</t>
-  </si>
-  <si>
-    <t>결론 문장만 — 숫자는 2120A</t>
-  </si>
-  <si>
-    <t>값 6칸</t>
-  </si>
-  <si>
-    <t>2120A</t>
-  </si>
-  <si>
-    <t>계획단계 분석적검토</t>
-  </si>
-  <si>
-    <t>당기 가결산 숫자 · 2차 화면 입력 후보</t>
-  </si>
-  <si>
     <t>값 1,053칸(숫자)</t>
   </si>
   <si>
@@ -319,24 +349,33 @@
     <t>감사위험의 평가</t>
   </si>
   <si>
-    <t>전기 평가 유지 + 당기 변화 반영</t>
+    <t>보통 그대로 · 일관성 점검 대상 — 2301·2302·2530·3100·3150 이 서로 맞아야 함</t>
+  </si>
+  <si>
+    <t>이월본 그대로 + 일관성 점검</t>
   </si>
   <si>
     <t>값 54칸</t>
   </si>
   <si>
+    <t>✓ 대화 안내: 보통 그대로, 상호 대사</t>
+  </si>
+  <si>
     <t>2302</t>
   </si>
   <si>
     <t>중요왜곡표시위험의 식별·평가 및 대응</t>
   </si>
   <si>
-    <t>계정별 위험은 이월, 잔액은 당기 숫자</t>
+    <t>기본 세팅: 유의적 위험 = 부정위험·매출. 계정 잔액만 당기 숫자 · 일관성 점검 대상 — 2301·2302·2530·3100·3150 이 서로 맞아야 함</t>
   </si>
   <si>
     <t>값 553칸</t>
   </si>
   <si>
+    <t>✓ 대화 안내: 보통 그대로, 유의적 위험 기본 세팅</t>
+  </si>
+  <si>
     <t>2511</t>
   </si>
   <si>
@@ -388,12 +427,15 @@
     <t>통제활동의 이해와 평가·통제 test</t>
   </si>
   <si>
-    <t>추적조사(walkthrough) 표본은 당기</t>
+    <t>비상장은 통제테스트를 하지 않음 — 이해·평가만 · 일관성 점검 대상 — 2301·2302·2530·3100·3150 이 서로 맞아야 함</t>
   </si>
   <si>
     <t>값 280칸</t>
   </si>
   <si>
+    <t>✓ 대화 안내: 비상장은 통제테스트 안 함</t>
+  </si>
+  <si>
     <t>2531</t>
   </si>
   <si>
@@ -421,7 +463,13 @@
     <t>내부회계관리제도 검토</t>
   </si>
   <si>
-    <t>내부회계 검토 대상 회사 · ★ 초안 도움</t>
+    <t>상장회사가 아니면 해당없음</t>
+  </si>
+  <si>
+    <t>대부분 상장회사가 아니면 해당 없음</t>
+  </si>
+  <si>
+    <t>✓ 수정의견: 상장 아니면 해당없음</t>
   </si>
   <si>
     <t>2700</t>
@@ -523,24 +571,30 @@
     <t>위험에 대한 대응</t>
   </si>
   <si>
-    <t>계정별 절차 매핑은 이월, 당기 보완</t>
+    <t>기본 세팅: 실증절차 위주 · 통제테스트 안 함 · 기말에 테스트 범위 확대. 회사 특화 문구만 손봄 · 일관성 점검 대상 — 2301·2302·2530·3100·3150 이 서로 맞아야 함</t>
   </si>
   <si>
     <t>머리 2025-12-26 · 값 475칸</t>
   </si>
   <si>
+    <t>✓ 대화 안내: 보통 그대로, 실증 위주</t>
+  </si>
+  <si>
     <t>3150</t>
   </si>
   <si>
     <t>통제테스트</t>
   </si>
   <si>
-    <t>통제에 의존할 때</t>
+    <t>통제에 의존할 때 — 비상장 기본은 해당없음 · 일관성 점검 대상 — 2301·2302·2530·3100·3150 이 서로 맞아야 함</t>
   </si>
   <si>
     <t>숨김</t>
   </si>
   <si>
+    <t>✓ 대화 안내: 통제테스트 안 함</t>
+  </si>
+  <si>
     <t>3200</t>
   </si>
   <si>
@@ -637,12 +691,15 @@
     <t>부정의 검토</t>
   </si>
   <si>
-    <t>질문 대상·일자, 답변 갱신</t>
+    <t>매년 전기와 같음</t>
   </si>
   <si>
     <t>머리 2026-03-23 · 값 95칸</t>
   </si>
   <si>
+    <t>✓ 대화 안내: 전기와 동일</t>
+  </si>
+  <si>
     <t>3600A·B·C</t>
   </si>
   <si>
@@ -748,9 +805,6 @@
     <t>후속사건의 검토</t>
   </si>
   <si>
-    <t>보고서일까지의 기간·날짜</t>
-  </si>
-  <si>
     <t>값 76칸</t>
   </si>
   <si>
@@ -811,7 +865,16 @@
     <t>심리사항점검표(품질관리리뷰어)</t>
   </si>
   <si>
-    <t>별도 파일 · 목록엔 있고 시트 없음</t>
+    <t>해당없음</t>
+  </si>
+  <si>
+    <t>심리실 소관 — 감사팀 조서가 아님</t>
+  </si>
+  <si>
+    <t>심리실 소관이라 해당사항 없는 것이 맞음</t>
+  </si>
+  <si>
+    <t>✓ 수정의견: 심리실 소관</t>
   </si>
   <si>
     <t>8600</t>
@@ -992,6 +1055,42 @@
   </si>
   <si>
     <t>★ 초안 도움 대상 = 회사 사업 이해(2100·2100A)와 내부통제·IT(2511~2532·2600)</t>
+  </si>
+  <si>
+    <t>일관성 규칙</t>
+  </si>
+  <si>
+    <t>위험평가 → 대응이 서로 맞아야 한다(사용자 안내 2026-09-26). 비상장 기본 세팅:</t>
+  </si>
+  <si>
+    <t>유의적 위험 = 부정위험 · 매출(수익인식). 이 기본에서 벗어나는 회사는 거의 없다</t>
+  </si>
+  <si>
+    <t>2530 · 3150</t>
+  </si>
+  <si>
+    <t>통제테스트를 하지 않는다 — 통제는 이해·평가만</t>
+  </si>
+  <si>
+    <t>실증절차 위주 · 통제위험에 대응해 기말에 테스트 범위를 넓힌다 · 회사 특화 문구만 손본다</t>
+  </si>
+  <si>
+    <t>다섯 조서의 선택이 어긋나면 이월 때 경고로 띄운다</t>
+  </si>
+  <si>
+    <t>샘플 기준</t>
+  </si>
+  <si>
+    <t>명진산업개발 FY2025 조서는 「소규모감사기준」 양식이다(재무제표는 일반기업회계기준)</t>
+  </si>
+  <si>
+    <t>2026-09-26 사용자</t>
+  </si>
+  <si>
+    <t>ERP 조서</t>
+  </si>
+  <si>
+    <t>1100·1100A·1200 은 인덕 ERP 에서 평가를 마친다 — 조서엔 「ERP 에서 수행함」</t>
   </si>
   <si>
     <t>단계 \ 갱신유형</t>
@@ -1013,7 +1112,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1026,26 +1125,31 @@
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF666666"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
@@ -1053,6 +1157,12 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1105,7 +1215,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1147,6 +1257,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1449,7 +1562,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K72"/>
+  <dimension ref="A1:L72"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1458,14 +1571,15 @@
     <col min="4" max="4" width="13" customWidth="1"/>
     <col min="5" max="5" width="9" customWidth="1"/>
     <col min="6" max="6" width="8" customWidth="1"/>
-    <col min="7" max="7" width="46" customWidth="1"/>
+    <col min="7" max="7" width="54" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="34" customWidth="1"/>
     <col min="9" max="9" width="30" customWidth="1"/>
     <col min="10" max="10" width="7" customWidth="1"/>
     <col min="11" max="11" width="34" customWidth="1"/>
+    <col min="12" max="12" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1499,122 +1613,128 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>11</v>
-      </c>
       <c r="E2" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G2" s="6"/>
       <c r="H2" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K2" s="7"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L2" s="6"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>11</v>
-      </c>
       <c r="E3" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" s="7"/>
+      <c r="L3" s="6"/>
+    </row>
+    <row r="4" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="K4" s="7"/>
+      <c r="L4" s="6"/>
+    </row>
+    <row r="5" spans="1:12" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K3" s="7"/>
-    </row>
-    <row r="4" spans="1:11" ht="25.5" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K4" s="7"/>
-    </row>
-    <row r="5" spans="1:11" ht="25.5" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>32</v>
-      </c>
       <c r="F5" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>33</v>
@@ -1626,108 +1746,130 @@
         <v>35</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K5" s="7"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I6" s="6" t="s">
         <v>42</v>
       </c>
       <c r="J6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="K6" s="7"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" s="6" t="s">
+      <c r="C7" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="D7" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I7" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="4" t="s">
+      <c r="J7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K7" s="7"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C8" s="6" t="s">
+      <c r="F8" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G8" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" s="6" t="s">
+      <c r="H8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="H8" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="I8" s="6" t="s">
+      <c r="J8" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="K8" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="L8" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="K8" s="7"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>52</v>
       </c>
@@ -1738,13 +1880,13 @@
         <v>54</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>55</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>56</v>
@@ -1756,2055 +1898,2147 @@
         <v>58</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="K9" s="7"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L9" s="6"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>52</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>55</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>57</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="K10" s="7"/>
-    </row>
-    <row r="11" spans="1:11" ht="25.5" x14ac:dyDescent="0.3">
+      <c r="L10" s="6"/>
+    </row>
+    <row r="11" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>52</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K11" s="7"/>
-    </row>
-    <row r="12" spans="1:11" ht="25.5" x14ac:dyDescent="0.3">
+      <c r="L11" s="6"/>
+    </row>
+    <row r="12" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>52</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C12" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="H12" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>34</v>
-      </c>
       <c r="I12" s="6" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K12" s="7"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L12" s="6"/>
+    </row>
+    <row r="13" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>52</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="K13" s="7"/>
-    </row>
-    <row r="14" spans="1:11" ht="25.5" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+      <c r="K13" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>52</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K14" s="7"/>
-    </row>
-    <row r="15" spans="1:11" ht="25.5" x14ac:dyDescent="0.3">
+      <c r="L14" s="6"/>
+    </row>
+    <row r="15" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>52</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>34</v>
+        <v>87</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="K15" s="7"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>52</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K16" s="7"/>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L16" s="6"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>52</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K17" s="7"/>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L17" s="6"/>
+    </row>
+    <row r="18" spans="1:12" ht="25.5" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>52</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>57</v>
+        <v>104</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="K18" s="7"/>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L18" s="6" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="25.5" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>52</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>57</v>
+        <v>104</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="K19" s="7"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L19" s="6" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>52</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="K20" s="7"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L20" s="6"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>52</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="K21" s="7"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L21" s="6"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>52</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="K22" s="7"/>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L22" s="6"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
         <v>52</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="K23" s="7"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L23" s="6"/>
+    </row>
+    <row r="24" spans="1:12" ht="25.5" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
         <v>52</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>57</v>
+        <v>104</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="K24" s="7"/>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L24" s="6" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
         <v>52</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="K25" s="7"/>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L25" s="6"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>52</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="K26" s="7"/>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L26" s="6"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
         <v>52</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>55</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="H27" s="6" t="s">
         <v>57</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="K27" s="7"/>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+      <c r="K27" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="L27" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>52</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K28" s="7"/>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L28" s="6"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
         <v>52</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K29" s="7"/>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L29" s="6"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
         <v>52</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K30" s="7"/>
-    </row>
-    <row r="31" spans="1:11" ht="25.5" x14ac:dyDescent="0.3">
+      <c r="L30" s="6"/>
+    </row>
+    <row r="31" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
         <v>52</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G31" s="6"/>
       <c r="H31" s="6" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K31" s="7"/>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L31" s="6"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
         <v>52</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G32" s="6"/>
       <c r="H32" s="6" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K32" s="7"/>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L32" s="6"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
         <v>52</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K33" s="7"/>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L33" s="6"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>52</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="F34" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="K34" s="7"/>
+      <c r="L34" s="6"/>
+    </row>
+    <row r="35" spans="1:12" ht="38.25" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E35" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G34" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="I34" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="J34" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K34" s="7"/>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>55</v>
-      </c>
       <c r="F35" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>57</v>
+        <v>104</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="K35" s="7"/>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L35" s="6" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="25.5" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>163</v>
+        <v>180</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="K36" s="7"/>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L36" s="6" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>170</v>
+        <v>188</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="K37" s="7"/>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L37" s="6"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G38" s="6"/>
       <c r="H38" s="6" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K38" s="7"/>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L38" s="6"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="B39" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="I39" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="J39" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="K39" s="7"/>
+      <c r="L39" s="6"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A40" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="C39" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G39" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="H39" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="I39" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="J39" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="K39" s="7"/>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A40" s="6" t="s">
-        <v>158</v>
-      </c>
       <c r="B40" s="6" t="s">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>178</v>
+        <v>196</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="E40" s="5" t="s">
         <v>55</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>179</v>
+        <v>197</v>
       </c>
       <c r="H40" s="6" t="s">
         <v>57</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="K40" s="7"/>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L40" s="6"/>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="E41" s="5" t="s">
         <v>55</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G41" s="6"/>
       <c r="H41" s="6" t="s">
         <v>57</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K41" s="7"/>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L41" s="6"/>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="E42" s="5" t="s">
         <v>55</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="H42" s="6" t="s">
         <v>57</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K42" s="7"/>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L42" s="6"/>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="6" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="E43" s="5" t="s">
         <v>55</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G43" s="6"/>
       <c r="H43" s="6" t="s">
         <v>57</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="K43" s="7"/>
-    </row>
-    <row r="44" spans="1:11" ht="25.5" x14ac:dyDescent="0.3">
+      <c r="L43" s="6"/>
+    </row>
+    <row r="44" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="E44" s="5" t="s">
         <v>55</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="H44" s="6" t="s">
         <v>57</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K44" s="7"/>
-    </row>
-    <row r="45" spans="1:11" ht="25.5" x14ac:dyDescent="0.3">
+      <c r="L44" s="6"/>
+    </row>
+    <row r="45" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="6" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>196</v>
+        <v>214</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="I45" s="6"/>
       <c r="J45" s="4" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="K45" s="7"/>
-    </row>
-    <row r="46" spans="1:11" ht="25.5" x14ac:dyDescent="0.3">
+      <c r="L45" s="6"/>
+    </row>
+    <row r="46" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="K46" s="7"/>
-    </row>
-    <row r="47" spans="1:11" ht="25.5" x14ac:dyDescent="0.3">
+      <c r="L46" s="6" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>196</v>
+        <v>214</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="I47" s="6"/>
       <c r="J47" s="4" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="K47" s="7"/>
-    </row>
-    <row r="48" spans="1:11" ht="25.5" x14ac:dyDescent="0.3">
+      <c r="L47" s="6"/>
+    </row>
+    <row r="48" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>203</v>
+        <v>222</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>204</v>
+        <v>223</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>205</v>
+        <v>224</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="K48" s="7"/>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L48" s="6"/>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>206</v>
+        <v>225</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>207</v>
+        <v>226</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="K49" s="7"/>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L49" s="6"/>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>210</v>
+        <v>229</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>211</v>
+        <v>230</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>212</v>
+        <v>231</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K50" s="7"/>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L50" s="6"/>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="6" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>214</v>
+        <v>233</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>215</v>
+        <v>234</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K51" s="7"/>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L51" s="6"/>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>216</v>
+        <v>235</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K52" s="7"/>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L52" s="6"/>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>220</v>
+        <v>239</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G53" s="6"/>
       <c r="H53" s="6" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="I53" s="6" t="s">
-        <v>222</v>
+        <v>241</v>
       </c>
       <c r="J53" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K53" s="7"/>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L53" s="6"/>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="6" t="s">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>223</v>
+        <v>242</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>224</v>
+        <v>243</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>225</v>
+        <v>244</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>226</v>
+        <v>245</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K54" s="7"/>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L54" s="6"/>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>227</v>
+        <v>246</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>228</v>
+        <v>247</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G55" s="6"/>
       <c r="H55" s="6" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="I55" s="6" t="s">
-        <v>229</v>
+        <v>248</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K55" s="7"/>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L55" s="6"/>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G56" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="H56" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="I56" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="J56" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="K56" s="7"/>
+      <c r="L56" s="6"/>
+    </row>
+    <row r="57" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G57" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="H57" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I57" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="J57" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="K57" s="7"/>
+      <c r="L57" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="B56" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="C56" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="D56" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="E56" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="F56" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G56" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="I56" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="J56" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K56" s="7"/>
-    </row>
-    <row r="57" spans="1:11" ht="25.5" x14ac:dyDescent="0.3">
-      <c r="A57" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="C57" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="D57" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="E57" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F57" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G57" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="H57" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="I57" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="J57" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="K57" s="7"/>
-    </row>
-    <row r="58" spans="1:11" ht="25.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="58" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="6" t="s">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="B58" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="H58" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="I58" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="J58" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="K58" s="7"/>
+      <c r="L58" s="6"/>
+    </row>
+    <row r="59" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="C58" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="D58" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="E58" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F58" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G58" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="I58" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="J58" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K58" s="7"/>
-    </row>
-    <row r="59" spans="1:11" ht="25.5" x14ac:dyDescent="0.3">
-      <c r="A59" s="6" t="s">
-        <v>219</v>
-      </c>
       <c r="B59" s="6" t="s">
-        <v>242</v>
+        <v>260</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G59" s="6" t="s">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="I59" s="6" t="s">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="K59" s="7"/>
-    </row>
-    <row r="60" spans="1:11" ht="25.5" x14ac:dyDescent="0.3">
+      <c r="L59" s="6"/>
+    </row>
+    <row r="60" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="6" t="s">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>247</v>
+        <v>265</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G60" s="6"/>
       <c r="H60" s="6" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="I60" s="6" t="s">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K60" s="7"/>
-    </row>
-    <row r="61" spans="1:11" ht="25.5" x14ac:dyDescent="0.3">
+      <c r="L60" s="6"/>
+    </row>
+    <row r="61" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="6" t="s">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>249</v>
+        <v>267</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G61" s="6" t="s">
-        <v>251</v>
+        <v>269</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="I61" s="6" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="K61" s="7"/>
-    </row>
-    <row r="62" spans="1:11" ht="25.5" x14ac:dyDescent="0.3">
+      <c r="L61" s="6"/>
+    </row>
+    <row r="62" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="6" t="s">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G62" s="6"/>
       <c r="H62" s="6" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="I62" s="6" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="J62" s="4" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="K62" s="7"/>
-    </row>
-    <row r="63" spans="1:11" ht="25.5" x14ac:dyDescent="0.3">
+      <c r="L62" s="6"/>
+    </row>
+    <row r="63" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="6" t="s">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>255</v>
+        <v>273</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>256</v>
+        <v>274</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>32</v>
+        <v>166</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>15</v>
+        <v>275</v>
       </c>
       <c r="G63" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="H63" s="6" t="s">
-        <v>34</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="H63" s="6"/>
       <c r="I63" s="6"/>
       <c r="J63" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="K63" s="7"/>
-    </row>
-    <row r="64" spans="1:11" ht="25.5" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+      <c r="K63" s="17" t="s">
+        <v>277</v>
+      </c>
+      <c r="L63" s="6" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="6" t="s">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>258</v>
+        <v>279</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>259</v>
+        <v>280</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>260</v>
+        <v>281</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="I64" s="6" t="s">
-        <v>261</v>
+        <v>282</v>
       </c>
       <c r="J64" s="4" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="K64" s="7"/>
-    </row>
-    <row r="65" spans="1:11" ht="25.5" x14ac:dyDescent="0.3">
+      <c r="L64" s="6"/>
+    </row>
+    <row r="65" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="6" t="s">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>262</v>
+        <v>283</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>263</v>
+        <v>284</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G65" s="6"/>
       <c r="H65" s="6" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="I65" s="6" t="s">
-        <v>264</v>
+        <v>285</v>
       </c>
       <c r="J65" s="4" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="K65" s="7"/>
-    </row>
-    <row r="66" spans="1:11" ht="25.5" x14ac:dyDescent="0.3">
+      <c r="L65" s="6"/>
+    </row>
+    <row r="66" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="6" t="s">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>265</v>
+        <v>286</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="I66" s="6" t="s">
-        <v>268</v>
+        <v>289</v>
       </c>
       <c r="J66" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K66" s="7"/>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L66" s="6"/>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" s="6" t="s">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>269</v>
+        <v>290</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G67" s="6" t="s">
-        <v>272</v>
+        <v>293</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>273</v>
+        <v>294</v>
       </c>
       <c r="I67" s="6" t="s">
-        <v>274</v>
+        <v>295</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="K67" s="7"/>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L67" s="6"/>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" s="6" t="s">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>275</v>
+        <v>296</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>277</v>
+        <v>298</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>273</v>
+        <v>294</v>
       </c>
       <c r="I68" s="6" t="s">
-        <v>274</v>
+        <v>295</v>
       </c>
       <c r="J68" s="4" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="K68" s="7"/>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L68" s="6"/>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" s="6" t="s">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>279</v>
+        <v>300</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G69" s="6"/>
       <c r="H69" s="6" t="s">
-        <v>273</v>
+        <v>294</v>
       </c>
       <c r="I69" s="6" t="s">
-        <v>274</v>
+        <v>295</v>
       </c>
       <c r="J69" s="4" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="K69" s="7"/>
-    </row>
-    <row r="70" spans="1:11" ht="25.5" x14ac:dyDescent="0.3">
+      <c r="L69" s="6"/>
+    </row>
+    <row r="70" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="6" t="s">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>280</v>
+        <v>301</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>281</v>
+        <v>302</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>282</v>
+        <v>303</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="I70" s="6" t="s">
-        <v>283</v>
+        <v>304</v>
       </c>
       <c r="J70" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K70" s="7"/>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L70" s="6"/>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>284</v>
+        <v>305</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>285</v>
+        <v>306</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G71" s="6" t="s">
-        <v>287</v>
+        <v>308</v>
       </c>
       <c r="H71" s="6"/>
       <c r="I71" s="6"/>
       <c r="J71" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K71" s="7"/>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L71" s="6"/>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" s="6" t="s">
-        <v>284</v>
+        <v>305</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>289</v>
+        <v>310</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>290</v>
+        <v>311</v>
       </c>
       <c r="H72" s="6"/>
       <c r="I72" s="6"/>
       <c r="J72" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K72" s="7"/>
+      <c r="L72" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K72" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:L72" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="6" type="noConversion"/>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" sqref="E2:E72" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -3820,7 +4054,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -3828,9 +4062,9 @@
     <col min="3" max="3" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -3840,24 +4074,24 @@
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
     </row>
-    <row r="3" spans="1:3" ht="25.5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
-        <v>292</v>
+        <v>313</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>293</v>
+        <v>314</v>
       </c>
       <c r="C3" s="10"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>295</v>
+        <v>316</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>296</v>
+        <v>317</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -3870,7 +4104,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>297</v>
+        <v>318</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>7</v>
@@ -3878,35 +4112,35 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>298</v>
+        <v>319</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>299</v>
+        <v>320</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>300</v>
+        <v>321</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -3914,7 +4148,7 @@
         <v>55</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>301</v>
+        <v>322</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>57</v>
@@ -3922,35 +4156,35 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>302</v>
+        <v>323</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>303</v>
+        <v>324</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>273</v>
+        <v>294</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>304</v>
+        <v>325</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -3963,41 +4197,41 @@
         <v>3</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>305</v>
+        <v>326</v>
       </c>
       <c r="C15" s="12"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>306</v>
+        <v>327</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>307</v>
+        <v>328</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>308</v>
+        <v>329</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>309</v>
+        <v>330</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>310</v>
+        <v>331</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>311</v>
+        <v>332</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -4007,39 +4241,116 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
-        <v>312</v>
+        <v>333</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>313</v>
+        <v>334</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="25.5" x14ac:dyDescent="0.3">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="9"/>
       <c r="B21" s="9" t="s">
-        <v>315</v>
+        <v>336</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="9"/>
       <c r="B22" s="9" t="s">
-        <v>316</v>
+        <v>337</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="9"/>
       <c r="B23" s="9" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="C23" s="9"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="9"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="C25" s="10"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="C26" s="9"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="C27" s="9"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="C28" s="9"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="C29" s="9"/>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="9"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>348</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
@@ -4058,49 +4369,49 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>318</v>
+        <v>351</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>55</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>319</v>
+        <v>352</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B2" s="4">
         <f>COUNTIFS('조서별 규칙'!$D$2:$D$72,"*계획*",'조서별 규칙'!$E$2:$E$72,"①")</f>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C2" s="4">
         <f>COUNTIFS('조서별 규칙'!$D$2:$D$72,"*계획*",'조서별 규칙'!$E$2:$E$72,"②")</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D2" s="4">
         <f>COUNTIFS('조서별 규칙'!$D$2:$D$72,"*계획*",'조서별 규칙'!$E$2:$E$72,"③")</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E2" s="4">
         <f>COUNTIFS('조서별 규칙'!$D$2:$D$72,"*계획*",'조서별 규칙'!$E$2:$E$72,"④")</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F2" s="4">
         <f>COUNTIFS('조서별 규칙'!$D$2:$D$72,"*계획*",'조서별 규칙'!$E$2:$E$72,"참고")</f>
@@ -4117,11 +4428,11 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="B3" s="4">
         <f>COUNTIFS('조서별 규칙'!$D$2:$D$72,"*중간*",'조서별 규칙'!$E$2:$E$72,"①")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" s="4">
         <f>COUNTIFS('조서별 규칙'!$D$2:$D$72,"*중간*",'조서별 규칙'!$E$2:$E$72,"②")</f>
@@ -4133,7 +4444,7 @@
       </c>
       <c r="E3" s="4">
         <f>COUNTIFS('조서별 규칙'!$D$2:$D$72,"*중간*",'조서별 규칙'!$E$2:$E$72,"④")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" s="4">
         <f>COUNTIFS('조서별 규칙'!$D$2:$D$72,"*중간*",'조서별 규칙'!$E$2:$E$72,"참고")</f>
@@ -4150,15 +4461,15 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="B4" s="4">
         <f>COUNTIFS('조서별 규칙'!$D$2:$D$72,"*기말*",'조서별 규칙'!$E$2:$E$72,"①")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C4" s="4">
         <f>COUNTIFS('조서별 규칙'!$D$2:$D$72,"*기말*",'조서별 규칙'!$E$2:$E$72,"②")</f>
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D4" s="4">
         <f>COUNTIFS('조서별 규칙'!$D$2:$D$72,"*기말*",'조서별 규칙'!$E$2:$E$72,"③")</f>
@@ -4178,28 +4489,28 @@
       </c>
       <c r="H4" s="4">
         <f>SUM(B4:G4)</f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
-        <v>319</v>
+        <v>352</v>
       </c>
       <c r="B5" s="5">
         <f t="shared" ref="B5:H5" si="0">SUM(B2:B4)</f>
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C5" s="5">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D5" s="5">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E5" s="5">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F5" s="5">
         <f t="shared" si="0"/>
@@ -4211,7 +4522,7 @@
       </c>
       <c r="H5" s="5">
         <f t="shared" si="0"/>
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -4226,11 +4537,11 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
-        <v>320</v>
+        <v>353</v>
       </c>
       <c r="B7" s="15">
         <f>D5+E5</f>
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C7" s="15"/>
       <c r="D7" s="15"/>
@@ -4241,11 +4552,11 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
-        <v>321</v>
+        <v>354</v>
       </c>
       <c r="B8" s="15">
         <f>B5+C5</f>
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C8" s="15"/>
       <c r="D8" s="15"/>
@@ -4256,7 +4567,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
-        <v>322</v>
+        <v>355</v>
       </c>
     </row>
   </sheetData>

--- a/docs/일반조서/일반조서_조서별규칙_초안.xlsx
+++ b/docs/일반조서/일반조서_조서별규칙_초안.xlsx
@@ -8,16 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\geniw\JAYTAX개발\docs\일반조서\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37105A1C-B419-43CB-883D-A5DD84294161}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1D09B50-75F3-4F7A-82CD-ABB67AB4FAA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12375" yWindow="2025" windowWidth="15330" windowHeight="10770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="조서별 규칙" sheetId="1" r:id="rId1"/>
     <sheet name="범례" sheetId="2" r:id="rId2"/>
     <sheet name="요약" sheetId="3" r:id="rId3"/>
+    <sheet name="일반 실측(알티스트)" sheetId="4" r:id="rId4"/>
+    <sheet name="K-IFRS 구성(윤성)" sheetId="5" r:id="rId5"/>
+    <sheet name="기준별 번호 차이" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'K-IFRS 구성(윤성)'!$A$1:$G$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'일반 실측(알티스트)'!$A$1:$M$67</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'조서별 규칙'!$A$1:$L$72</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
@@ -38,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1848" uniqueCount="483">
   <si>
     <t>섹션</t>
   </si>
@@ -1106,13 +1111,394 @@
   </si>
   <si>
     <t>주: 여러 단계에 걸친 조서(2700·2700A)는 각 단계에 한 번씩 셉니다. 적용 「조건부」도 포함한 숫자입니다.</t>
+  </si>
+  <si>
+    <t>시트</t>
+  </si>
+  <si>
+    <t>조서명(감사조서목록)</t>
+  </si>
+  <si>
+    <t>수행여부</t>
+  </si>
+  <si>
+    <t>머리 작성일 FY25</t>
+  </si>
+  <si>
+    <t>단계(날짜로)</t>
+  </si>
+  <si>
+    <t>바뀐 칸</t>
+  </si>
+  <si>
+    <t>전체 칸</t>
+  </si>
+  <si>
+    <t>변경률%</t>
+  </si>
+  <si>
+    <t>숫자 비중</t>
+  </si>
+  <si>
+    <t>실측 제안</t>
+  </si>
+  <si>
+    <t>초안 유형(소규모 규칙)</t>
+  </si>
+  <si>
+    <t>비고</t>
+  </si>
+  <si>
+    <t>회사가 더한 시트(코드 없음)</t>
+  </si>
+  <si>
+    <t>조서작성업무흐름 및 유의사항</t>
+  </si>
+  <si>
+    <t>감사조서목록</t>
+  </si>
+  <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
+    <t>2025-04-28, 2025-12-31</t>
+  </si>
+  <si>
+    <t>⚠️ 1000번대는 기준마다 번호 뜻이 다르다 — 초안 유형 비교 무의미</t>
+  </si>
+  <si>
+    <t>1300</t>
+  </si>
+  <si>
+    <t>초안 ④ ↔ 실측 ①</t>
+  </si>
+  <si>
+    <t>kick-off meeting 회의록</t>
+  </si>
+  <si>
+    <t>2025-12-31, 2025-04-28</t>
+  </si>
+  <si>
+    <t>초안 ② ↔ 실측 ①</t>
+  </si>
+  <si>
+    <t>2120B(재무비율분석)</t>
+  </si>
+  <si>
+    <t>2120B</t>
+  </si>
+  <si>
+    <t>숨김 — 해당없음</t>
+  </si>
+  <si>
+    <t>2132</t>
+  </si>
+  <si>
+    <t>2133</t>
+  </si>
+  <si>
+    <t>2025-10-12, 2025-12-31</t>
+  </si>
+  <si>
+    <t>2026-02-18, 2025-12-31</t>
+  </si>
+  <si>
+    <t>초안 ③ ↔ 실측 ①</t>
+  </si>
+  <si>
+    <t>참고 시트 — 번호가 소규모 계획단계(2700A-1)와 겹친다</t>
+  </si>
+  <si>
+    <t>2700A-2(감사계획단계)</t>
+  </si>
+  <si>
+    <t>2700A-3(감사수행단계)</t>
+  </si>
+  <si>
+    <t>2700A-4(감사완결단계)</t>
+  </si>
+  <si>
+    <t>2700A-4</t>
+  </si>
+  <si>
+    <t>양정기준(중요성)</t>
+  </si>
+  <si>
+    <t>초안 ④ ↔ 실측 ③</t>
+  </si>
+  <si>
+    <t>특수관계자</t>
+  </si>
+  <si>
+    <t>초안 ③ ↔ 실측 ②</t>
+  </si>
+  <si>
+    <t>3900A</t>
+  </si>
+  <si>
+    <t>3900B</t>
+  </si>
+  <si>
+    <t>3910A</t>
+  </si>
+  <si>
+    <t>3910B</t>
+  </si>
+  <si>
+    <t>3910C</t>
+  </si>
+  <si>
+    <t>8110A</t>
+  </si>
+  <si>
+    <t>2025-02-18, 2024-12-31</t>
+  </si>
+  <si>
+    <t>읽는 법</t>
+  </si>
+  <si>
+    <t>머리(1~8행)를 뺀 칸을 FY2024 와 FY2025 사이에 한 칸씩 비교했다. 변경률 0 = 한 글자도 안 바뀜.</t>
+  </si>
+  <si>
+    <t>실측 제안: 0~3% ① · 숫자 위주로 9%↑ ③ · 글자 위주로 30%↑ ④ · 그 밖 ②. 기계적 제안이라 사람이 확정한다.</t>
+  </si>
+  <si>
+    <t>단계: 머리 작성일 2025-04-28=계획 · 2025-10-12=중간 · 2026-02-18=기말(알티스트 FY25).</t>
+  </si>
+  <si>
+    <t>파일(섹션)</t>
+  </si>
+  <si>
+    <t>보임</t>
+  </si>
+  <si>
+    <t>칸 수</t>
+  </si>
+  <si>
+    <t>머리 작성일</t>
+  </si>
+  <si>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>섹션 파일마다 반복되는 공통 시트</t>
+  </si>
+  <si>
+    <t>조서작성업무흐름도</t>
+  </si>
+  <si>
+    <t>기본사항</t>
+  </si>
+  <si>
+    <t>2025-06-30</t>
+  </si>
+  <si>
+    <t>2000</t>
+  </si>
+  <si>
+    <t>2025-08-05, 2025-08-05</t>
+  </si>
+  <si>
+    <t>조직도</t>
+  </si>
+  <si>
+    <t>2025-08-05, 2025-12-31</t>
+  </si>
+  <si>
+    <t>2025-04-06, 2025-04-06</t>
+  </si>
+  <si>
+    <t>요약</t>
+  </si>
+  <si>
+    <t>주요공시내역</t>
+  </si>
+  <si>
+    <t>전환사채 주요내역</t>
+  </si>
+  <si>
+    <t>2025-07-11</t>
+  </si>
+  <si>
+    <t>2110B</t>
+  </si>
+  <si>
+    <t>2025-07-11, 2025-07-11</t>
+  </si>
+  <si>
+    <t>1000 파일에도 있음</t>
+  </si>
+  <si>
+    <t>2530A-1</t>
+  </si>
+  <si>
+    <t>2530A-2</t>
+  </si>
+  <si>
+    <t>2530A-3</t>
+  </si>
+  <si>
+    <t>2530A-4</t>
+  </si>
+  <si>
+    <t>2530A-5</t>
+  </si>
+  <si>
+    <t>2530B-1</t>
+  </si>
+  <si>
+    <t>2530B-2</t>
+  </si>
+  <si>
+    <t>2530B-3</t>
+  </si>
+  <si>
+    <t>3000</t>
+  </si>
+  <si>
+    <t>2000 파일에도 있음 — 단계마다 다시 씀</t>
+  </si>
+  <si>
+    <t>2026-02-20, 2025-12-31</t>
+  </si>
+  <si>
+    <t>2026-02-20, 2026-02-20</t>
+  </si>
+  <si>
+    <t>특수관계자 거래 검토</t>
+  </si>
+  <si>
+    <t>2026-06-23, 2025-12-31</t>
+  </si>
+  <si>
+    <t>3900C</t>
+  </si>
+  <si>
+    <t>3900D</t>
+  </si>
+  <si>
+    <t>2026-06-23, 2021-12-31</t>
+  </si>
+  <si>
+    <t>⚠️ 머리 날짜가 몇 해 전 그대로</t>
+  </si>
+  <si>
+    <t>8110ARP_BS</t>
+  </si>
+  <si>
+    <t>2025-06-30, 2026-06-23</t>
+  </si>
+  <si>
+    <t>8110ARP_PL</t>
+  </si>
+  <si>
+    <t>2026-06-23, 2026-06-23</t>
+  </si>
+  <si>
+    <t>2022-08-05, 2025-12-31</t>
+  </si>
+  <si>
+    <t>8000</t>
+  </si>
+  <si>
+    <t>3000 파일에도 있음</t>
+  </si>
+  <si>
+    <t>A500_FY25Q4</t>
+  </si>
+  <si>
+    <t>정산표</t>
+  </si>
+  <si>
+    <t>2025-12-31, 2024-12-31</t>
+  </si>
+  <si>
+    <t>2026-02-20</t>
+  </si>
+  <si>
+    <t>2022-08-05, 2022-08-05</t>
+  </si>
+  <si>
+    <t>3000 파일에도 있음 · ⚠️ 머리 날짜가 몇 해 전 그대로</t>
+  </si>
+  <si>
+    <t>소규모(명진 FY25)</t>
+  </si>
+  <si>
+    <t>일반(알티스트 FY25)</t>
+  </si>
+  <si>
+    <t>K-IFRS(윤성 FY25)</t>
+  </si>
+  <si>
+    <t>계약전 위험평가에 대한 재검토</t>
+  </si>
+  <si>
+    <t>계약전 위험평가</t>
+  </si>
+  <si>
+    <t>소규모는 두 조서가 하나로 합쳐져 있다</t>
+  </si>
+  <si>
+    <t>독립성·윤리규정·품질관리기준 준수</t>
+  </si>
+  <si>
+    <t>감사업무조건의 합의</t>
+  </si>
+  <si>
+    <t>⚠️ 같은 번호, 다른 조서</t>
+  </si>
+  <si>
+    <t>(없음)</t>
+  </si>
+  <si>
+    <t>소규모 1200 = 일반·K-IFRS 1300</t>
+  </si>
+  <si>
+    <t>중요성 산정 — 계획단계</t>
+  </si>
+  <si>
+    <t>⚠️ 알티스트만 한 칸 밀린다(계획 A-2 · 수행 A-3 · 완결 A-4). 기준보다 양식 판(연도) 차이로 보인다</t>
+  </si>
+  <si>
+    <t>중요성 산정 — 수행단계</t>
+  </si>
+  <si>
+    <t>중요성 산정 — 완결단계</t>
+  </si>
+  <si>
+    <t>⚠️ 윤성은 8600 이 감사종료</t>
+  </si>
+  <si>
+    <t>시산표(목록에만, 시트 없음)</t>
+  </si>
+  <si>
+    <t>⚠️</t>
+  </si>
+  <si>
+    <t>8800·8810·8820</t>
+  </si>
+  <si>
+    <t>시산표 · 날인 재무제표 · 감사보고서</t>
+  </si>
+  <si>
+    <t>(확인 안 함)</t>
+  </si>
+  <si>
+    <t>8700·8710·8720 으로 한 칸 앞</t>
+  </si>
+  <si>
+    <t>⚠️ 첨부 번호도 다르다</t>
+  </si>
+  <si>
+    <t>결론: 같은 번호가 기준·양식 판에 따라 다른 조서다. 조서 규칙은 기준 × 양식 연도별로 두고, 이월·기준 전환은 번호가 아니라 시트 제목(조서명)으로 짝짓는다.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1164,8 +1550,29 @@
       <family val="2"/>
       <charset val="129"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF555555"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1187,8 +1594,23 @@
         <fgColor rgb="FFE9EFF7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F3A5F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDE9D9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1211,11 +1633,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC8CED8"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFC8CED8"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFC8CED8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFC8CED8"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1260,6 +1697,26 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -2183,7 +2640,7 @@
       <c r="K17" s="7"/>
       <c r="L17" s="6"/>
     </row>
-    <row r="18" spans="1:12" ht="25.5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>52</v>
       </c>
@@ -2219,7 +2676,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="25.5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>52</v>
       </c>
@@ -2391,7 +2848,7 @@
       <c r="K23" s="7"/>
       <c r="L23" s="6"/>
     </row>
-    <row r="24" spans="1:12" ht="25.5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
         <v>52</v>
       </c>
@@ -2767,7 +3224,7 @@
       <c r="K34" s="7"/>
       <c r="L34" s="6"/>
     </row>
-    <row r="35" spans="1:12" ht="38.25" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>174</v>
       </c>
@@ -2803,7 +3260,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="25.5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
         <v>174</v>
       </c>
@@ -4574,4 +5031,5122 @@
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:M71"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="9" width="8" customWidth="1"/>
+    <col min="10" max="11" width="9" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
+    <col min="13" max="13" width="44" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="25.5" x14ac:dyDescent="0.3">
+      <c r="A1" s="18" t="s">
+        <v>356</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>357</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>358</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>359</v>
+      </c>
+      <c r="F1" s="18" t="s">
+        <v>360</v>
+      </c>
+      <c r="G1" s="18" t="s">
+        <v>361</v>
+      </c>
+      <c r="H1" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="I1" s="18" t="s">
+        <v>363</v>
+      </c>
+      <c r="J1" s="18" t="s">
+        <v>364</v>
+      </c>
+      <c r="K1" s="18" t="s">
+        <v>365</v>
+      </c>
+      <c r="L1" s="18" t="s">
+        <v>366</v>
+      </c>
+      <c r="M1" s="18" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20">
+        <v>0</v>
+      </c>
+      <c r="H2" s="20">
+        <v>1</v>
+      </c>
+      <c r="I2" s="21">
+        <v>0</v>
+      </c>
+      <c r="J2" s="20"/>
+      <c r="K2" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="L2" s="20"/>
+      <c r="M2" s="19" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20">
+        <v>2</v>
+      </c>
+      <c r="H3" s="20">
+        <v>22</v>
+      </c>
+      <c r="I3" s="20">
+        <v>9.1</v>
+      </c>
+      <c r="J3" s="20">
+        <v>0.5</v>
+      </c>
+      <c r="K3" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="L3" s="20"/>
+      <c r="M3" s="19" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="25.5" x14ac:dyDescent="0.3">
+      <c r="A4" s="19" t="s">
+        <v>369</v>
+      </c>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20">
+        <v>0</v>
+      </c>
+      <c r="H4" s="20">
+        <v>61</v>
+      </c>
+      <c r="I4" s="21">
+        <v>0</v>
+      </c>
+      <c r="J4" s="20"/>
+      <c r="K4" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="L4" s="20"/>
+      <c r="M4" s="19" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" s="19" t="s">
+        <v>370</v>
+      </c>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="19" t="s">
+        <v>371</v>
+      </c>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20">
+        <v>32</v>
+      </c>
+      <c r="H5" s="20">
+        <v>233</v>
+      </c>
+      <c r="I5" s="20">
+        <v>13.2</v>
+      </c>
+      <c r="J5" s="20">
+        <v>0.72</v>
+      </c>
+      <c r="K5" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="L5" s="20"/>
+      <c r="M5" s="19" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="25.5" x14ac:dyDescent="0.3">
+      <c r="A6" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="19"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="20">
+        <v>31</v>
+      </c>
+      <c r="H6" s="20">
+        <v>99</v>
+      </c>
+      <c r="I6" s="20">
+        <v>31.3</v>
+      </c>
+      <c r="J6" s="20">
+        <v>0.97</v>
+      </c>
+      <c r="K6" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="L6" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="M6" s="19" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="25.5" x14ac:dyDescent="0.3">
+      <c r="A7" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="19"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" s="20">
+        <v>1</v>
+      </c>
+      <c r="H7" s="20">
+        <v>34</v>
+      </c>
+      <c r="I7" s="20">
+        <v>2.9</v>
+      </c>
+      <c r="J7" s="20">
+        <v>0</v>
+      </c>
+      <c r="K7" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="L7" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="M7" s="19" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8" s="19" t="s">
+        <v>374</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>374</v>
+      </c>
+      <c r="C8" s="19"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="F8" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" s="20">
+        <v>2</v>
+      </c>
+      <c r="H8" s="20">
+        <v>15</v>
+      </c>
+      <c r="I8" s="20">
+        <v>13.3</v>
+      </c>
+      <c r="J8" s="20">
+        <v>0</v>
+      </c>
+      <c r="K8" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="L8" s="20"/>
+      <c r="M8" s="19"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" s="19"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" s="20">
+        <v>0</v>
+      </c>
+      <c r="H9" s="20">
+        <v>23</v>
+      </c>
+      <c r="I9" s="21">
+        <v>0</v>
+      </c>
+      <c r="J9" s="20"/>
+      <c r="K9" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="L9" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="M9" s="23" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="C10" s="19"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="F10" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" s="20">
+        <v>296</v>
+      </c>
+      <c r="H10" s="20">
+        <v>236</v>
+      </c>
+      <c r="I10" s="20">
+        <v>92.2</v>
+      </c>
+      <c r="J10" s="20">
+        <v>0.15</v>
+      </c>
+      <c r="K10" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="L10" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="M10" s="19"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A11" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="C11" s="19"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" s="20">
+        <v>15</v>
+      </c>
+      <c r="H11" s="20">
+        <v>246</v>
+      </c>
+      <c r="I11" s="20">
+        <v>6.1</v>
+      </c>
+      <c r="J11" s="20">
+        <v>0.33</v>
+      </c>
+      <c r="K11" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="L11" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="M11" s="19"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" s="19"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="F12" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" s="20">
+        <v>9</v>
+      </c>
+      <c r="H12" s="20">
+        <v>101</v>
+      </c>
+      <c r="I12" s="20">
+        <v>8.9</v>
+      </c>
+      <c r="J12" s="20">
+        <v>0.44</v>
+      </c>
+      <c r="K12" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="L12" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="M12" s="19"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13" s="19" t="s">
+        <v>376</v>
+      </c>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20">
+        <v>4</v>
+      </c>
+      <c r="H13" s="20">
+        <v>94</v>
+      </c>
+      <c r="I13" s="20">
+        <v>4.3</v>
+      </c>
+      <c r="J13" s="20">
+        <v>0.25</v>
+      </c>
+      <c r="K13" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="L13" s="20"/>
+      <c r="M13" s="19" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A14" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14" s="19"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="19" t="s">
+        <v>377</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="G14" s="20">
+        <v>0</v>
+      </c>
+      <c r="H14" s="20">
+        <v>235</v>
+      </c>
+      <c r="I14" s="21">
+        <v>0</v>
+      </c>
+      <c r="J14" s="20"/>
+      <c r="K14" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="L14" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="M14" s="23" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A15" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="C15" s="19"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="F15" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="G15" s="20">
+        <v>0</v>
+      </c>
+      <c r="H15" s="20">
+        <v>79</v>
+      </c>
+      <c r="I15" s="21">
+        <v>0</v>
+      </c>
+      <c r="J15" s="20"/>
+      <c r="K15" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="L15" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="M15" s="23" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A16" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="C16" s="19"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="F16" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="G16" s="20">
+        <v>1233</v>
+      </c>
+      <c r="H16" s="20">
+        <v>1315</v>
+      </c>
+      <c r="I16" s="20">
+        <v>79.400000000000006</v>
+      </c>
+      <c r="J16" s="20">
+        <v>0.61</v>
+      </c>
+      <c r="K16" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="L16" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="M16" s="19"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A17" s="19" t="s">
+        <v>379</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>380</v>
+      </c>
+      <c r="C17" s="19"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20">
+        <v>0</v>
+      </c>
+      <c r="H17" s="20">
+        <v>89</v>
+      </c>
+      <c r="I17" s="21">
+        <v>0</v>
+      </c>
+      <c r="J17" s="20"/>
+      <c r="K17" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="L17" s="20"/>
+      <c r="M17" s="19" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A18" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="C18" s="19"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="F18" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="G18" s="20">
+        <v>0</v>
+      </c>
+      <c r="H18" s="20">
+        <v>28</v>
+      </c>
+      <c r="I18" s="21">
+        <v>0</v>
+      </c>
+      <c r="J18" s="20"/>
+      <c r="K18" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="L18" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="M18" s="19"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A19" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="C19" s="19"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="F19" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="G19" s="20">
+        <v>1</v>
+      </c>
+      <c r="H19" s="20">
+        <v>32</v>
+      </c>
+      <c r="I19" s="20">
+        <v>3.1</v>
+      </c>
+      <c r="J19" s="20">
+        <v>0</v>
+      </c>
+      <c r="K19" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="L19" s="20"/>
+      <c r="M19" s="19"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A20" s="19" t="s">
+        <v>383</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>383</v>
+      </c>
+      <c r="C20" s="19"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="F20" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="G20" s="20">
+        <v>0</v>
+      </c>
+      <c r="H20" s="20">
+        <v>52</v>
+      </c>
+      <c r="I20" s="21">
+        <v>0</v>
+      </c>
+      <c r="J20" s="20"/>
+      <c r="K20" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="L20" s="20"/>
+      <c r="M20" s="19"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A21" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="C21" s="19"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="F21" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="G21" s="20">
+        <v>0</v>
+      </c>
+      <c r="H21" s="20">
+        <v>54</v>
+      </c>
+      <c r="I21" s="21">
+        <v>0</v>
+      </c>
+      <c r="J21" s="20"/>
+      <c r="K21" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="L21" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="M21" s="19"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A22" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C22" s="19"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="G22" s="20">
+        <v>0</v>
+      </c>
+      <c r="H22" s="20">
+        <v>553</v>
+      </c>
+      <c r="I22" s="21">
+        <v>0</v>
+      </c>
+      <c r="J22" s="20"/>
+      <c r="K22" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="L22" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="M22" s="19"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A23" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="C23" s="19"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="19" t="s">
+        <v>384</v>
+      </c>
+      <c r="F23" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="G23" s="20">
+        <v>0</v>
+      </c>
+      <c r="H23" s="20">
+        <v>91</v>
+      </c>
+      <c r="I23" s="21">
+        <v>0</v>
+      </c>
+      <c r="J23" s="20"/>
+      <c r="K23" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="L23" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="M23" s="19"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A24" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="C24" s="19"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="19" t="s">
+        <v>384</v>
+      </c>
+      <c r="F24" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="G24" s="20">
+        <v>0</v>
+      </c>
+      <c r="H24" s="20">
+        <v>43</v>
+      </c>
+      <c r="I24" s="21">
+        <v>0</v>
+      </c>
+      <c r="J24" s="20"/>
+      <c r="K24" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="L24" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="M24" s="19"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A25" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="C25" s="19"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="19" t="s">
+        <v>384</v>
+      </c>
+      <c r="F25" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="G25" s="20">
+        <v>0</v>
+      </c>
+      <c r="H25" s="20">
+        <v>42</v>
+      </c>
+      <c r="I25" s="21">
+        <v>0</v>
+      </c>
+      <c r="J25" s="20"/>
+      <c r="K25" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="L25" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="M25" s="19"/>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A26" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="B26" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="C26" s="19"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="19" t="s">
+        <v>384</v>
+      </c>
+      <c r="F26" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="G26" s="20">
+        <v>0</v>
+      </c>
+      <c r="H26" s="20">
+        <v>191</v>
+      </c>
+      <c r="I26" s="21">
+        <v>0</v>
+      </c>
+      <c r="J26" s="20"/>
+      <c r="K26" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="L26" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="M26" s="19"/>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A27" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="C27" s="19"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="19" t="s">
+        <v>384</v>
+      </c>
+      <c r="F27" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="G27" s="20">
+        <v>0</v>
+      </c>
+      <c r="H27" s="20">
+        <v>280</v>
+      </c>
+      <c r="I27" s="21">
+        <v>0</v>
+      </c>
+      <c r="J27" s="20"/>
+      <c r="K27" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="L27" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="M27" s="19"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A28" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="C28" s="19"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="19" t="s">
+        <v>384</v>
+      </c>
+      <c r="F28" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="G28" s="20">
+        <v>0</v>
+      </c>
+      <c r="H28" s="20">
+        <v>405</v>
+      </c>
+      <c r="I28" s="21">
+        <v>0</v>
+      </c>
+      <c r="J28" s="20"/>
+      <c r="K28" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="L28" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="M28" s="23" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A29" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="B29" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="C29" s="19"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="19" t="s">
+        <v>385</v>
+      </c>
+      <c r="F29" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="G29" s="20">
+        <v>0</v>
+      </c>
+      <c r="H29" s="20">
+        <v>15</v>
+      </c>
+      <c r="I29" s="21">
+        <v>0</v>
+      </c>
+      <c r="J29" s="20"/>
+      <c r="K29" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="L29" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="M29" s="23" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A30" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="B30" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="C30" s="19"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="19" t="s">
+        <v>384</v>
+      </c>
+      <c r="F30" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="G30" s="20">
+        <v>9</v>
+      </c>
+      <c r="H30" s="20">
+        <v>56</v>
+      </c>
+      <c r="I30" s="20">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="J30" s="20">
+        <v>1</v>
+      </c>
+      <c r="K30" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="L30" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="M30" s="19"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A31" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="B31" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="C31" s="19"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20">
+        <v>0</v>
+      </c>
+      <c r="H31" s="20">
+        <v>108</v>
+      </c>
+      <c r="I31" s="21">
+        <v>0</v>
+      </c>
+      <c r="J31" s="20"/>
+      <c r="K31" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="L31" s="20"/>
+      <c r="M31" s="19" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A32" s="19" t="s">
+        <v>388</v>
+      </c>
+      <c r="B32" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="C32" s="19"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="19" t="s">
+        <v>384</v>
+      </c>
+      <c r="F32" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="G32" s="20">
+        <v>9</v>
+      </c>
+      <c r="H32" s="20">
+        <v>100</v>
+      </c>
+      <c r="I32" s="20">
+        <v>9</v>
+      </c>
+      <c r="J32" s="20">
+        <v>0.89</v>
+      </c>
+      <c r="K32" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="L32" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="M32" s="19"/>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A33" s="19" t="s">
+        <v>389</v>
+      </c>
+      <c r="B33" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="C33" s="19"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="19" t="s">
+        <v>385</v>
+      </c>
+      <c r="F33" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="G33" s="20">
+        <v>23</v>
+      </c>
+      <c r="H33" s="20">
+        <v>101</v>
+      </c>
+      <c r="I33" s="20">
+        <v>22.8</v>
+      </c>
+      <c r="J33" s="20">
+        <v>0.96</v>
+      </c>
+      <c r="K33" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="L33" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="M33" s="19"/>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A34" s="19" t="s">
+        <v>390</v>
+      </c>
+      <c r="B34" s="19" t="s">
+        <v>391</v>
+      </c>
+      <c r="C34" s="19"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="19" t="s">
+        <v>385</v>
+      </c>
+      <c r="F34" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="G34" s="20">
+        <v>23</v>
+      </c>
+      <c r="H34" s="20">
+        <v>101</v>
+      </c>
+      <c r="I34" s="20">
+        <v>22.8</v>
+      </c>
+      <c r="J34" s="20">
+        <v>0.96</v>
+      </c>
+      <c r="K34" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="L34" s="20"/>
+      <c r="M34" s="19"/>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A35" s="19" t="s">
+        <v>392</v>
+      </c>
+      <c r="B35" s="19"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="19"/>
+      <c r="F35" s="20"/>
+      <c r="G35" s="20">
+        <v>24</v>
+      </c>
+      <c r="H35" s="20">
+        <v>179</v>
+      </c>
+      <c r="I35" s="20">
+        <v>13.4</v>
+      </c>
+      <c r="J35" s="20">
+        <v>1</v>
+      </c>
+      <c r="K35" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="L35" s="20"/>
+      <c r="M35" s="19" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A36" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="B36" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="C36" s="19"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="19" t="s">
+        <v>384</v>
+      </c>
+      <c r="F36" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="G36" s="20">
+        <v>3</v>
+      </c>
+      <c r="H36" s="20">
+        <v>475</v>
+      </c>
+      <c r="I36" s="20">
+        <v>0.6</v>
+      </c>
+      <c r="J36" s="20">
+        <v>0</v>
+      </c>
+      <c r="K36" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="L36" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="M36" s="19"/>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A37" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="B37" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="C37" s="19"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="19" t="s">
+        <v>385</v>
+      </c>
+      <c r="F37" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="G37" s="20">
+        <v>0</v>
+      </c>
+      <c r="H37" s="20">
+        <v>30</v>
+      </c>
+      <c r="I37" s="21">
+        <v>0</v>
+      </c>
+      <c r="J37" s="20"/>
+      <c r="K37" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="L37" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="M37" s="23" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A38" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="B38" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="C38" s="19"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="19" t="s">
+        <v>385</v>
+      </c>
+      <c r="F38" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="G38" s="20">
+        <v>0</v>
+      </c>
+      <c r="H38" s="20">
+        <v>11</v>
+      </c>
+      <c r="I38" s="21">
+        <v>0</v>
+      </c>
+      <c r="J38" s="20"/>
+      <c r="K38" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="L38" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="M38" s="23" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A39" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="B39" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="C39" s="19"/>
+      <c r="D39" s="20"/>
+      <c r="E39" s="19" t="s">
+        <v>371</v>
+      </c>
+      <c r="F39" s="20"/>
+      <c r="G39" s="20">
+        <v>0</v>
+      </c>
+      <c r="H39" s="20">
+        <v>26</v>
+      </c>
+      <c r="I39" s="21">
+        <v>0</v>
+      </c>
+      <c r="J39" s="20"/>
+      <c r="K39" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="L39" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="M39" s="19" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A40" s="19" t="s">
+        <v>195</v>
+      </c>
+      <c r="B40" s="19" t="s">
+        <v>195</v>
+      </c>
+      <c r="C40" s="19"/>
+      <c r="D40" s="20"/>
+      <c r="E40" s="19" t="s">
+        <v>384</v>
+      </c>
+      <c r="F40" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="G40" s="20">
+        <v>1</v>
+      </c>
+      <c r="H40" s="20">
+        <v>78</v>
+      </c>
+      <c r="I40" s="20">
+        <v>1.3</v>
+      </c>
+      <c r="J40" s="20">
+        <v>0</v>
+      </c>
+      <c r="K40" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="L40" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="M40" s="23" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A41" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="B41" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="C41" s="19"/>
+      <c r="D41" s="20"/>
+      <c r="E41" s="19" t="s">
+        <v>385</v>
+      </c>
+      <c r="F41" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="G41" s="20">
+        <v>0</v>
+      </c>
+      <c r="H41" s="20">
+        <v>83</v>
+      </c>
+      <c r="I41" s="21">
+        <v>0</v>
+      </c>
+      <c r="J41" s="20"/>
+      <c r="K41" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="L41" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="M41" s="23" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A42" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="B42" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="C42" s="19"/>
+      <c r="D42" s="20"/>
+      <c r="E42" s="19" t="s">
+        <v>385</v>
+      </c>
+      <c r="F42" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="G42" s="20">
+        <v>97</v>
+      </c>
+      <c r="H42" s="20">
+        <v>87</v>
+      </c>
+      <c r="I42" s="20">
+        <v>64.7</v>
+      </c>
+      <c r="J42" s="20">
+        <v>0.06</v>
+      </c>
+      <c r="K42" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="L42" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="M42" s="19"/>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A43" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="B43" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="C43" s="19"/>
+      <c r="D43" s="20"/>
+      <c r="E43" s="19" t="s">
+        <v>385</v>
+      </c>
+      <c r="F43" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="G43" s="20">
+        <v>23</v>
+      </c>
+      <c r="H43" s="20">
+        <v>98</v>
+      </c>
+      <c r="I43" s="20">
+        <v>22.5</v>
+      </c>
+      <c r="J43" s="20">
+        <v>0.96</v>
+      </c>
+      <c r="K43" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="L43" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="M43" s="23" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A44" s="19" t="s">
+        <v>394</v>
+      </c>
+      <c r="B44" s="19"/>
+      <c r="C44" s="19"/>
+      <c r="D44" s="20"/>
+      <c r="E44" s="19"/>
+      <c r="F44" s="20"/>
+      <c r="G44" s="20">
+        <v>156</v>
+      </c>
+      <c r="H44" s="20">
+        <v>122</v>
+      </c>
+      <c r="I44" s="20">
+        <v>94</v>
+      </c>
+      <c r="J44" s="20">
+        <v>0.47</v>
+      </c>
+      <c r="K44" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="L44" s="20"/>
+      <c r="M44" s="19" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A45" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="B45" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="C45" s="19"/>
+      <c r="D45" s="20"/>
+      <c r="E45" s="19" t="s">
+        <v>385</v>
+      </c>
+      <c r="F45" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="G45" s="20">
+        <v>0</v>
+      </c>
+      <c r="H45" s="20">
+        <v>95</v>
+      </c>
+      <c r="I45" s="21">
+        <v>0</v>
+      </c>
+      <c r="J45" s="20"/>
+      <c r="K45" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="L45" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="M45" s="19"/>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A46" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="B46" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="C46" s="19"/>
+      <c r="D46" s="20"/>
+      <c r="E46" s="19" t="s">
+        <v>371</v>
+      </c>
+      <c r="F46" s="20"/>
+      <c r="G46" s="20">
+        <v>0</v>
+      </c>
+      <c r="H46" s="20">
+        <v>21</v>
+      </c>
+      <c r="I46" s="21">
+        <v>0</v>
+      </c>
+      <c r="J46" s="20"/>
+      <c r="K46" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="L46" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="M46" s="19" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A47" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="B47" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="C47" s="19"/>
+      <c r="D47" s="20"/>
+      <c r="E47" s="19" t="s">
+        <v>385</v>
+      </c>
+      <c r="F47" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="G47" s="20">
+        <v>5</v>
+      </c>
+      <c r="H47" s="20">
+        <v>84</v>
+      </c>
+      <c r="I47" s="20">
+        <v>6</v>
+      </c>
+      <c r="J47" s="20">
+        <v>0</v>
+      </c>
+      <c r="K47" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="L47" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="M47" s="23" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A48" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="B48" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="C48" s="19"/>
+      <c r="D48" s="20"/>
+      <c r="E48" s="19" t="s">
+        <v>371</v>
+      </c>
+      <c r="F48" s="20"/>
+      <c r="G48" s="20">
+        <v>0</v>
+      </c>
+      <c r="H48" s="20">
+        <v>33</v>
+      </c>
+      <c r="I48" s="21">
+        <v>0</v>
+      </c>
+      <c r="J48" s="20"/>
+      <c r="K48" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="L48" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="M48" s="19" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A49" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="B49" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="C49" s="19"/>
+      <c r="D49" s="20"/>
+      <c r="E49" s="19" t="s">
+        <v>371</v>
+      </c>
+      <c r="F49" s="20"/>
+      <c r="G49" s="20">
+        <v>0</v>
+      </c>
+      <c r="H49" s="20">
+        <v>54</v>
+      </c>
+      <c r="I49" s="21">
+        <v>0</v>
+      </c>
+      <c r="J49" s="20"/>
+      <c r="K49" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="L49" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="M49" s="19" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A50" s="19" t="s">
+        <v>396</v>
+      </c>
+      <c r="B50" s="19" t="s">
+        <v>396</v>
+      </c>
+      <c r="C50" s="19"/>
+      <c r="D50" s="20"/>
+      <c r="E50" s="19" t="s">
+        <v>371</v>
+      </c>
+      <c r="F50" s="20"/>
+      <c r="G50" s="20">
+        <v>0</v>
+      </c>
+      <c r="H50" s="20">
+        <v>54</v>
+      </c>
+      <c r="I50" s="21">
+        <v>0</v>
+      </c>
+      <c r="J50" s="20"/>
+      <c r="K50" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="L50" s="20"/>
+      <c r="M50" s="19" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A51" s="19" t="s">
+        <v>397</v>
+      </c>
+      <c r="B51" s="19" t="s">
+        <v>397</v>
+      </c>
+      <c r="C51" s="19"/>
+      <c r="D51" s="20"/>
+      <c r="E51" s="19" t="s">
+        <v>371</v>
+      </c>
+      <c r="F51" s="20"/>
+      <c r="G51" s="20">
+        <v>0</v>
+      </c>
+      <c r="H51" s="20">
+        <v>3</v>
+      </c>
+      <c r="I51" s="21">
+        <v>0</v>
+      </c>
+      <c r="J51" s="20"/>
+      <c r="K51" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="L51" s="20"/>
+      <c r="M51" s="19" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A52" s="19" t="s">
+        <v>235</v>
+      </c>
+      <c r="B52" s="19" t="s">
+        <v>235</v>
+      </c>
+      <c r="C52" s="19"/>
+      <c r="D52" s="20"/>
+      <c r="E52" s="19" t="s">
+        <v>371</v>
+      </c>
+      <c r="F52" s="20"/>
+      <c r="G52" s="20">
+        <v>0</v>
+      </c>
+      <c r="H52" s="20">
+        <v>41</v>
+      </c>
+      <c r="I52" s="21">
+        <v>0</v>
+      </c>
+      <c r="J52" s="20"/>
+      <c r="K52" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="L52" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="M52" s="19" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A53" s="19" t="s">
+        <v>398</v>
+      </c>
+      <c r="B53" s="19" t="s">
+        <v>398</v>
+      </c>
+      <c r="C53" s="19"/>
+      <c r="D53" s="20"/>
+      <c r="E53" s="19" t="s">
+        <v>371</v>
+      </c>
+      <c r="F53" s="20"/>
+      <c r="G53" s="20">
+        <v>0</v>
+      </c>
+      <c r="H53" s="20">
+        <v>11</v>
+      </c>
+      <c r="I53" s="21">
+        <v>0</v>
+      </c>
+      <c r="J53" s="20"/>
+      <c r="K53" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="L53" s="20"/>
+      <c r="M53" s="19" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A54" s="19" t="s">
+        <v>399</v>
+      </c>
+      <c r="B54" s="19" t="s">
+        <v>399</v>
+      </c>
+      <c r="C54" s="19"/>
+      <c r="D54" s="20"/>
+      <c r="E54" s="19" t="s">
+        <v>371</v>
+      </c>
+      <c r="F54" s="20"/>
+      <c r="G54" s="20">
+        <v>0</v>
+      </c>
+      <c r="H54" s="20">
+        <v>68</v>
+      </c>
+      <c r="I54" s="21">
+        <v>0</v>
+      </c>
+      <c r="J54" s="20"/>
+      <c r="K54" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="L54" s="20"/>
+      <c r="M54" s="19" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A55" s="19" t="s">
+        <v>400</v>
+      </c>
+      <c r="B55" s="19" t="s">
+        <v>400</v>
+      </c>
+      <c r="C55" s="19"/>
+      <c r="D55" s="20"/>
+      <c r="E55" s="19" t="s">
+        <v>371</v>
+      </c>
+      <c r="F55" s="20"/>
+      <c r="G55" s="20">
+        <v>0</v>
+      </c>
+      <c r="H55" s="20">
+        <v>2</v>
+      </c>
+      <c r="I55" s="21">
+        <v>0</v>
+      </c>
+      <c r="J55" s="20"/>
+      <c r="K55" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="L55" s="20"/>
+      <c r="M55" s="19" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A56" s="19" t="s">
+        <v>239</v>
+      </c>
+      <c r="B56" s="19" t="s">
+        <v>239</v>
+      </c>
+      <c r="C56" s="19"/>
+      <c r="D56" s="20"/>
+      <c r="E56" s="19" t="s">
+        <v>385</v>
+      </c>
+      <c r="F56" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="G56" s="20">
+        <v>0</v>
+      </c>
+      <c r="H56" s="20">
+        <v>19</v>
+      </c>
+      <c r="I56" s="21">
+        <v>0</v>
+      </c>
+      <c r="J56" s="20"/>
+      <c r="K56" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="L56" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="M56" s="23" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A57" s="19" t="s">
+        <v>242</v>
+      </c>
+      <c r="B57" s="19" t="s">
+        <v>242</v>
+      </c>
+      <c r="C57" s="19"/>
+      <c r="D57" s="20"/>
+      <c r="E57" s="19"/>
+      <c r="F57" s="20"/>
+      <c r="G57" s="20">
+        <v>0</v>
+      </c>
+      <c r="H57" s="20">
+        <v>104</v>
+      </c>
+      <c r="I57" s="21">
+        <v>0</v>
+      </c>
+      <c r="J57" s="20"/>
+      <c r="K57" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="L57" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="M57" s="23" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A58" s="19" t="s">
+        <v>246</v>
+      </c>
+      <c r="B58" s="19" t="s">
+        <v>246</v>
+      </c>
+      <c r="C58" s="19"/>
+      <c r="D58" s="20"/>
+      <c r="E58" s="19" t="s">
+        <v>385</v>
+      </c>
+      <c r="F58" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="G58" s="20">
+        <v>0</v>
+      </c>
+      <c r="H58" s="20">
+        <v>58</v>
+      </c>
+      <c r="I58" s="21">
+        <v>0</v>
+      </c>
+      <c r="J58" s="20"/>
+      <c r="K58" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="L58" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="M58" s="23" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A59" s="19" t="s">
+        <v>401</v>
+      </c>
+      <c r="B59" s="19" t="s">
+        <v>401</v>
+      </c>
+      <c r="C59" s="19"/>
+      <c r="D59" s="20"/>
+      <c r="E59" s="19" t="s">
+        <v>402</v>
+      </c>
+      <c r="F59" s="20"/>
+      <c r="G59" s="20">
+        <v>286</v>
+      </c>
+      <c r="H59" s="20">
+        <v>513</v>
+      </c>
+      <c r="I59" s="20">
+        <v>53.9</v>
+      </c>
+      <c r="J59" s="20">
+        <v>0.88</v>
+      </c>
+      <c r="K59" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="L59" s="20"/>
+      <c r="M59" s="19"/>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A60" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="B60" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="C60" s="19"/>
+      <c r="D60" s="20"/>
+      <c r="E60" s="19" t="s">
+        <v>385</v>
+      </c>
+      <c r="F60" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="G60" s="20">
+        <v>1</v>
+      </c>
+      <c r="H60" s="20">
+        <v>76</v>
+      </c>
+      <c r="I60" s="20">
+        <v>1.3</v>
+      </c>
+      <c r="J60" s="20">
+        <v>0</v>
+      </c>
+      <c r="K60" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="L60" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="M60" s="19"/>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A61" s="19" t="s">
+        <v>256</v>
+      </c>
+      <c r="B61" s="19" t="s">
+        <v>256</v>
+      </c>
+      <c r="C61" s="19"/>
+      <c r="D61" s="20"/>
+      <c r="E61" s="19" t="s">
+        <v>385</v>
+      </c>
+      <c r="F61" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="G61" s="20">
+        <v>0</v>
+      </c>
+      <c r="H61" s="20">
+        <v>12</v>
+      </c>
+      <c r="I61" s="21">
+        <v>0</v>
+      </c>
+      <c r="J61" s="20"/>
+      <c r="K61" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="L61" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="M61" s="23" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A62" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="B62" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="C62" s="19"/>
+      <c r="D62" s="20"/>
+      <c r="E62" s="19" t="s">
+        <v>385</v>
+      </c>
+      <c r="F62" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="G62" s="20">
+        <v>0</v>
+      </c>
+      <c r="H62" s="20">
+        <v>50</v>
+      </c>
+      <c r="I62" s="21">
+        <v>0</v>
+      </c>
+      <c r="J62" s="20"/>
+      <c r="K62" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="L62" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="M62" s="23" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A63" s="19" t="s">
+        <v>267</v>
+      </c>
+      <c r="B63" s="19" t="s">
+        <v>267</v>
+      </c>
+      <c r="C63" s="19"/>
+      <c r="D63" s="20"/>
+      <c r="E63" s="19"/>
+      <c r="F63" s="20"/>
+      <c r="G63" s="20">
+        <v>0</v>
+      </c>
+      <c r="H63" s="20">
+        <v>0</v>
+      </c>
+      <c r="I63" s="21">
+        <v>0</v>
+      </c>
+      <c r="J63" s="20"/>
+      <c r="K63" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="L63" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="M63" s="23" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A64" s="19" t="s">
+        <v>271</v>
+      </c>
+      <c r="B64" s="19" t="s">
+        <v>271</v>
+      </c>
+      <c r="C64" s="19"/>
+      <c r="D64" s="20"/>
+      <c r="E64" s="19"/>
+      <c r="F64" s="20"/>
+      <c r="G64" s="20">
+        <v>0</v>
+      </c>
+      <c r="H64" s="20">
+        <v>0</v>
+      </c>
+      <c r="I64" s="21">
+        <v>0</v>
+      </c>
+      <c r="J64" s="20"/>
+      <c r="K64" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="L64" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="M64" s="23" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A65" s="19" t="s">
+        <v>279</v>
+      </c>
+      <c r="B65" s="19" t="s">
+        <v>279</v>
+      </c>
+      <c r="C65" s="19"/>
+      <c r="D65" s="20"/>
+      <c r="E65" s="19" t="s">
+        <v>385</v>
+      </c>
+      <c r="F65" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="G65" s="20">
+        <v>0</v>
+      </c>
+      <c r="H65" s="20">
+        <v>48</v>
+      </c>
+      <c r="I65" s="21">
+        <v>0</v>
+      </c>
+      <c r="J65" s="20"/>
+      <c r="K65" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="L65" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="M65" s="23" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A66" s="19" t="s">
+        <v>283</v>
+      </c>
+      <c r="B66" s="19" t="s">
+        <v>283</v>
+      </c>
+      <c r="C66" s="19"/>
+      <c r="D66" s="20"/>
+      <c r="E66" s="19"/>
+      <c r="F66" s="20"/>
+      <c r="G66" s="20">
+        <v>0</v>
+      </c>
+      <c r="H66" s="20">
+        <v>1</v>
+      </c>
+      <c r="I66" s="21">
+        <v>0</v>
+      </c>
+      <c r="J66" s="20"/>
+      <c r="K66" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="L66" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="M66" s="23" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A67" s="19" t="s">
+        <v>286</v>
+      </c>
+      <c r="B67" s="19" t="s">
+        <v>286</v>
+      </c>
+      <c r="C67" s="19"/>
+      <c r="D67" s="20"/>
+      <c r="E67" s="19" t="s">
+        <v>385</v>
+      </c>
+      <c r="F67" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="G67" s="20">
+        <v>1</v>
+      </c>
+      <c r="H67" s="20">
+        <v>198</v>
+      </c>
+      <c r="I67" s="20">
+        <v>0.5</v>
+      </c>
+      <c r="J67" s="20">
+        <v>0</v>
+      </c>
+      <c r="K67" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="L67" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="M67" s="23" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A69" s="24" t="s">
+        <v>403</v>
+      </c>
+      <c r="B69" s="24"/>
+      <c r="C69" s="24" t="s">
+        <v>404</v>
+      </c>
+      <c r="D69" s="24"/>
+      <c r="E69" s="24"/>
+      <c r="F69" s="24"/>
+      <c r="G69" s="24"/>
+      <c r="H69" s="24"/>
+      <c r="I69" s="24"/>
+      <c r="J69" s="24"/>
+      <c r="K69" s="24"/>
+      <c r="L69" s="24"/>
+      <c r="M69" s="24"/>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A70" s="24"/>
+      <c r="B70" s="24"/>
+      <c r="C70" s="24" t="s">
+        <v>405</v>
+      </c>
+      <c r="D70" s="24"/>
+      <c r="E70" s="24"/>
+      <c r="F70" s="24"/>
+      <c r="G70" s="24"/>
+      <c r="H70" s="24"/>
+      <c r="I70" s="24"/>
+      <c r="J70" s="24"/>
+      <c r="K70" s="24"/>
+      <c r="L70" s="24"/>
+      <c r="M70" s="24"/>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A71" s="24"/>
+      <c r="B71" s="24"/>
+      <c r="C71" s="24" t="s">
+        <v>406</v>
+      </c>
+      <c r="D71" s="24"/>
+      <c r="E71" s="24"/>
+      <c r="F71" s="24"/>
+      <c r="G71" s="24"/>
+      <c r="H71" s="24"/>
+      <c r="I71" s="24"/>
+      <c r="J71" s="24"/>
+      <c r="K71" s="24"/>
+      <c r="L71" s="24"/>
+      <c r="M71" s="24"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:M67" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:G127"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="8" customWidth="1"/>
+    <col min="5" max="5" width="7" customWidth="1"/>
+    <col min="6" max="6" width="24" customWidth="1"/>
+    <col min="7" max="7" width="50" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="18" t="s">
+        <v>407</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>356</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>408</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>409</v>
+      </c>
+      <c r="F1" s="18" t="s">
+        <v>410</v>
+      </c>
+      <c r="G1" s="18" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="20" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="19"/>
+      <c r="D2" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E2" s="20">
+        <v>1</v>
+      </c>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="20" t="s">
+        <v>411</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="19"/>
+      <c r="D3" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E3" s="20">
+        <v>25</v>
+      </c>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="20" t="s">
+        <v>411</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>413</v>
+      </c>
+      <c r="C4" s="19"/>
+      <c r="D4" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E4" s="20">
+        <v>46</v>
+      </c>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="20" t="s">
+        <v>411</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="C5" s="19"/>
+      <c r="D5" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E5" s="20">
+        <v>316</v>
+      </c>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="20" t="s">
+        <v>411</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>370</v>
+      </c>
+      <c r="C6" s="19"/>
+      <c r="D6" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E6" s="20">
+        <v>227</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>415</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="20" t="s">
+        <v>411</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E7" s="20">
+        <v>12</v>
+      </c>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="20" t="s">
+        <v>411</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E8" s="20">
+        <v>33</v>
+      </c>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="20" t="s">
+        <v>411</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>374</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>374</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E9" s="20">
+        <v>15</v>
+      </c>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="20" t="s">
+        <v>411</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="E10" s="20">
+        <v>551</v>
+      </c>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="20" t="s">
+        <v>411</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>379</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>380</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="E11" s="20">
+        <v>89</v>
+      </c>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="19"/>
+      <c r="D12" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E12" s="20">
+        <v>1</v>
+      </c>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="19"/>
+      <c r="D13" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E13" s="20">
+        <v>25</v>
+      </c>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>413</v>
+      </c>
+      <c r="C14" s="19"/>
+      <c r="D14" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E14" s="20">
+        <v>46</v>
+      </c>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="C15" s="19"/>
+      <c r="D15" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E15" s="20">
+        <v>316</v>
+      </c>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>370</v>
+      </c>
+      <c r="C16" s="19"/>
+      <c r="D16" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E16" s="20">
+        <v>227</v>
+      </c>
+      <c r="F16" s="19" t="s">
+        <v>415</v>
+      </c>
+      <c r="G16" s="19" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E17" s="20">
+        <v>23</v>
+      </c>
+      <c r="F17" s="19" t="s">
+        <v>417</v>
+      </c>
+      <c r="G17" s="19"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E18" s="20">
+        <v>220</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>417</v>
+      </c>
+      <c r="G18" s="19"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>418</v>
+      </c>
+      <c r="C19" s="19"/>
+      <c r="D19" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E19" s="20">
+        <v>0</v>
+      </c>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E20" s="20">
+        <v>230</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>417</v>
+      </c>
+      <c r="G20" s="19"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E21" s="20">
+        <v>86</v>
+      </c>
+      <c r="F21" s="19" t="s">
+        <v>419</v>
+      </c>
+      <c r="G21" s="19"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E22" s="20">
+        <v>164</v>
+      </c>
+      <c r="F22" s="19" t="s">
+        <v>420</v>
+      </c>
+      <c r="G22" s="19"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>376</v>
+      </c>
+      <c r="C23" s="19"/>
+      <c r="D23" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E23" s="20">
+        <v>3</v>
+      </c>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>421</v>
+      </c>
+      <c r="C24" s="19"/>
+      <c r="D24" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E24" s="20">
+        <v>918</v>
+      </c>
+      <c r="F24" s="19"/>
+      <c r="G24" s="19" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>422</v>
+      </c>
+      <c r="C25" s="19"/>
+      <c r="D25" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E25" s="20">
+        <v>70</v>
+      </c>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="B26" s="19" t="s">
+        <v>423</v>
+      </c>
+      <c r="C26" s="19"/>
+      <c r="D26" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E26" s="20">
+        <v>989</v>
+      </c>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="C27" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="D27" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E27" s="20">
+        <v>120</v>
+      </c>
+      <c r="F27" s="19" t="s">
+        <v>424</v>
+      </c>
+      <c r="G27" s="19"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>425</v>
+      </c>
+      <c r="C28" s="19" t="s">
+        <v>425</v>
+      </c>
+      <c r="D28" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E28" s="20">
+        <v>84</v>
+      </c>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="B29" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="C29" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="D29" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E29" s="20">
+        <v>73</v>
+      </c>
+      <c r="F29" s="19" t="s">
+        <v>426</v>
+      </c>
+      <c r="G29" s="19"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="B30" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="C30" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="D30" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="E30" s="20">
+        <v>487</v>
+      </c>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="B31" s="19" t="s">
+        <v>379</v>
+      </c>
+      <c r="C31" s="19" t="s">
+        <v>380</v>
+      </c>
+      <c r="D31" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="E31" s="20">
+        <v>89</v>
+      </c>
+      <c r="F31" s="19"/>
+      <c r="G31" s="19" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="B32" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="C32" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="D32" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E32" s="20">
+        <v>28</v>
+      </c>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="B33" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="C33" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="D33" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E33" s="20">
+        <v>38</v>
+      </c>
+      <c r="F33" s="19"/>
+      <c r="G33" s="19"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="B34" s="19" t="s">
+        <v>383</v>
+      </c>
+      <c r="C34" s="19" t="s">
+        <v>383</v>
+      </c>
+      <c r="D34" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E34" s="20">
+        <v>66</v>
+      </c>
+      <c r="F34" s="19"/>
+      <c r="G34" s="19"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="B35" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="C35" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="D35" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E35" s="20">
+        <v>41</v>
+      </c>
+      <c r="F35" s="19"/>
+      <c r="G35" s="19"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="B36" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C36" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="D36" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E36" s="20">
+        <v>557</v>
+      </c>
+      <c r="F36" s="19"/>
+      <c r="G36" s="19"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="B37" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="C37" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="D37" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E37" s="20">
+        <v>91</v>
+      </c>
+      <c r="F37" s="19"/>
+      <c r="G37" s="19"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="B38" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="C38" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="D38" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E38" s="20">
+        <v>43</v>
+      </c>
+      <c r="F38" s="19"/>
+      <c r="G38" s="19"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="B39" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="C39" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="D39" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E39" s="20">
+        <v>42</v>
+      </c>
+      <c r="F39" s="19"/>
+      <c r="G39" s="19"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="B40" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="C40" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="D40" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E40" s="20">
+        <v>191</v>
+      </c>
+      <c r="F40" s="19"/>
+      <c r="G40" s="19"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="B41" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="C41" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="D41" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E41" s="20">
+        <v>271</v>
+      </c>
+      <c r="F41" s="19"/>
+      <c r="G41" s="19"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="B42" s="19" t="s">
+        <v>428</v>
+      </c>
+      <c r="C42" s="19" t="s">
+        <v>428</v>
+      </c>
+      <c r="D42" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E42" s="20">
+        <v>50</v>
+      </c>
+      <c r="F42" s="19"/>
+      <c r="G42" s="19"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="B43" s="19" t="s">
+        <v>429</v>
+      </c>
+      <c r="C43" s="19" t="s">
+        <v>429</v>
+      </c>
+      <c r="D43" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E43" s="20">
+        <v>40</v>
+      </c>
+      <c r="F43" s="19"/>
+      <c r="G43" s="19"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="B44" s="19" t="s">
+        <v>430</v>
+      </c>
+      <c r="C44" s="19" t="s">
+        <v>430</v>
+      </c>
+      <c r="D44" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E44" s="20">
+        <v>70</v>
+      </c>
+      <c r="F44" s="19"/>
+      <c r="G44" s="19"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="B45" s="19" t="s">
+        <v>431</v>
+      </c>
+      <c r="C45" s="19" t="s">
+        <v>431</v>
+      </c>
+      <c r="D45" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E45" s="20">
+        <v>70</v>
+      </c>
+      <c r="F45" s="19"/>
+      <c r="G45" s="19"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="B46" s="19" t="s">
+        <v>432</v>
+      </c>
+      <c r="C46" s="19" t="s">
+        <v>432</v>
+      </c>
+      <c r="D46" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E46" s="20">
+        <v>40</v>
+      </c>
+      <c r="F46" s="19"/>
+      <c r="G46" s="19"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="B47" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="C47" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="D47" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E47" s="20">
+        <v>52</v>
+      </c>
+      <c r="F47" s="19"/>
+      <c r="G47" s="19"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="B48" s="19" t="s">
+        <v>434</v>
+      </c>
+      <c r="C48" s="19" t="s">
+        <v>434</v>
+      </c>
+      <c r="D48" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E48" s="20">
+        <v>62</v>
+      </c>
+      <c r="F48" s="19"/>
+      <c r="G48" s="19"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="B49" s="19" t="s">
+        <v>435</v>
+      </c>
+      <c r="C49" s="19" t="s">
+        <v>435</v>
+      </c>
+      <c r="D49" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E49" s="20">
+        <v>32</v>
+      </c>
+      <c r="F49" s="19"/>
+      <c r="G49" s="19"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="B50" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="C50" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="D50" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E50" s="20">
+        <v>448</v>
+      </c>
+      <c r="F50" s="19"/>
+      <c r="G50" s="19"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="B51" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="C51" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D51" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E51" s="20">
+        <v>27</v>
+      </c>
+      <c r="F51" s="19" t="s">
+        <v>417</v>
+      </c>
+      <c r="G51" s="19"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="B52" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="C52" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="D52" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E52" s="20">
+        <v>53</v>
+      </c>
+      <c r="F52" s="19" t="s">
+        <v>417</v>
+      </c>
+      <c r="G52" s="19"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="B53" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="C53" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="D53" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E53" s="20">
+        <v>93</v>
+      </c>
+      <c r="F53" s="19" t="s">
+        <v>417</v>
+      </c>
+      <c r="G53" s="19"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A54" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="B54" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="C54" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="D54" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E54" s="20">
+        <v>87</v>
+      </c>
+      <c r="F54" s="19"/>
+      <c r="G54" s="19"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A55" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="B55" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="C55" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="D55" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E55" s="20">
+        <v>87</v>
+      </c>
+      <c r="F55" s="19" t="s">
+        <v>417</v>
+      </c>
+      <c r="G55" s="19"/>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A56" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="B56" s="19" t="s">
+        <v>392</v>
+      </c>
+      <c r="C56" s="19"/>
+      <c r="D56" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E56" s="20">
+        <v>179</v>
+      </c>
+      <c r="F56" s="19"/>
+      <c r="G56" s="19" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A57" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="B57" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="C57" s="19"/>
+      <c r="D57" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E57" s="20">
+        <v>1</v>
+      </c>
+      <c r="F57" s="19"/>
+      <c r="G57" s="19" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A58" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="B58" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C58" s="19"/>
+      <c r="D58" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E58" s="20">
+        <v>25</v>
+      </c>
+      <c r="F58" s="19"/>
+      <c r="G58" s="19" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A59" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="B59" s="19" t="s">
+        <v>413</v>
+      </c>
+      <c r="C59" s="19"/>
+      <c r="D59" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E59" s="20">
+        <v>46</v>
+      </c>
+      <c r="F59" s="19"/>
+      <c r="G59" s="19" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A60" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="B60" s="19" t="s">
+        <v>370</v>
+      </c>
+      <c r="C60" s="19"/>
+      <c r="D60" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E60" s="20">
+        <v>227</v>
+      </c>
+      <c r="F60" s="19" t="s">
+        <v>371</v>
+      </c>
+      <c r="G60" s="19" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A61" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="B61" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="C61" s="19"/>
+      <c r="D61" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E61" s="20">
+        <v>316</v>
+      </c>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A62" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="B62" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="C62" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="D62" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="E62" s="20">
+        <v>487</v>
+      </c>
+      <c r="F62" s="19"/>
+      <c r="G62" s="19" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A63" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="B63" s="19" t="s">
+        <v>379</v>
+      </c>
+      <c r="C63" s="19" t="s">
+        <v>380</v>
+      </c>
+      <c r="D63" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="E63" s="20">
+        <v>89</v>
+      </c>
+      <c r="F63" s="19"/>
+      <c r="G63" s="19" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A64" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="B64" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="C64" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D64" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E64" s="20">
+        <v>27</v>
+      </c>
+      <c r="F64" s="19" t="s">
+        <v>417</v>
+      </c>
+      <c r="G64" s="19" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A65" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="B65" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="C65" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="D65" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E65" s="20">
+        <v>53</v>
+      </c>
+      <c r="F65" s="19" t="s">
+        <v>419</v>
+      </c>
+      <c r="G65" s="19" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A66" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="B66" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="C66" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="D66" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E66" s="20">
+        <v>93</v>
+      </c>
+      <c r="F66" s="19" t="s">
+        <v>419</v>
+      </c>
+      <c r="G66" s="19" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A67" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="B67" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="C67" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="D67" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E67" s="20">
+        <v>91</v>
+      </c>
+      <c r="F67" s="19" t="s">
+        <v>371</v>
+      </c>
+      <c r="G67" s="19" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A68" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="B68" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="C68" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="D68" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E68" s="20">
+        <v>91</v>
+      </c>
+      <c r="F68" s="19" t="s">
+        <v>419</v>
+      </c>
+      <c r="G68" s="19" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A69" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="B69" s="19" t="s">
+        <v>392</v>
+      </c>
+      <c r="C69" s="19"/>
+      <c r="D69" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E69" s="20">
+        <v>179</v>
+      </c>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A70" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="B70" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="C70" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="D70" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E70" s="20">
+        <v>474</v>
+      </c>
+      <c r="F70" s="19"/>
+      <c r="G70" s="19"/>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A71" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="B71" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="C71" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="D71" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E71" s="20">
+        <v>28</v>
+      </c>
+      <c r="F71" s="19"/>
+      <c r="G71" s="19"/>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A72" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="B72" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="C72" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="D72" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E72" s="20">
+        <v>9</v>
+      </c>
+      <c r="F72" s="19" t="s">
+        <v>371</v>
+      </c>
+      <c r="G72" s="19"/>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A73" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="B73" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="C73" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="D73" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E73" s="20">
+        <v>26</v>
+      </c>
+      <c r="F73" s="19" t="s">
+        <v>371</v>
+      </c>
+      <c r="G73" s="19"/>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A74" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="B74" s="19" t="s">
+        <v>195</v>
+      </c>
+      <c r="C74" s="19" t="s">
+        <v>195</v>
+      </c>
+      <c r="D74" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E74" s="20">
+        <v>83</v>
+      </c>
+      <c r="F74" s="19" t="s">
+        <v>438</v>
+      </c>
+      <c r="G74" s="19"/>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A75" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="B75" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="C75" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="D75" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E75" s="20">
+        <v>95</v>
+      </c>
+      <c r="F75" s="19" t="s">
+        <v>439</v>
+      </c>
+      <c r="G75" s="19"/>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A76" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="B76" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="C76" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="D76" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E76" s="20">
+        <v>107</v>
+      </c>
+      <c r="F76" s="19" t="s">
+        <v>438</v>
+      </c>
+      <c r="G76" s="19"/>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A77" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="B77" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="C77" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="D77" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E77" s="20">
+        <v>36</v>
+      </c>
+      <c r="F77" s="19" t="s">
+        <v>439</v>
+      </c>
+      <c r="G77" s="19"/>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A78" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="B78" s="19" t="s">
+        <v>440</v>
+      </c>
+      <c r="C78" s="19"/>
+      <c r="D78" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E78" s="20">
+        <v>417</v>
+      </c>
+      <c r="F78" s="19"/>
+      <c r="G78" s="19" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A79" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="B79" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="C79" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="D79" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E79" s="20">
+        <v>95</v>
+      </c>
+      <c r="F79" s="19" t="s">
+        <v>439</v>
+      </c>
+      <c r="G79" s="19"/>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A80" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="B80" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="C80" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="D80" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E80" s="20">
+        <v>88</v>
+      </c>
+      <c r="F80" s="19" t="s">
+        <v>438</v>
+      </c>
+      <c r="G80" s="19"/>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A81" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="B81" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="C81" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="D81" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E81" s="20">
+        <v>33</v>
+      </c>
+      <c r="F81" s="19" t="s">
+        <v>441</v>
+      </c>
+      <c r="G81" s="19"/>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A82" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="B82" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="C82" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="D82" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E82" s="20">
+        <v>55</v>
+      </c>
+      <c r="F82" s="19" t="s">
+        <v>441</v>
+      </c>
+      <c r="G82" s="19"/>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A83" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="B83" s="19" t="s">
+        <v>396</v>
+      </c>
+      <c r="C83" s="19" t="s">
+        <v>396</v>
+      </c>
+      <c r="D83" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E83" s="20">
+        <v>24</v>
+      </c>
+      <c r="F83" s="19" t="s">
+        <v>441</v>
+      </c>
+      <c r="G83" s="19"/>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A84" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="B84" s="19" t="s">
+        <v>397</v>
+      </c>
+      <c r="C84" s="19" t="s">
+        <v>397</v>
+      </c>
+      <c r="D84" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E84" s="20">
+        <v>70</v>
+      </c>
+      <c r="F84" s="19" t="s">
+        <v>441</v>
+      </c>
+      <c r="G84" s="19"/>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A85" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="B85" s="19" t="s">
+        <v>442</v>
+      </c>
+      <c r="C85" s="19" t="s">
+        <v>442</v>
+      </c>
+      <c r="D85" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E85" s="20">
+        <v>3</v>
+      </c>
+      <c r="F85" s="19" t="s">
+        <v>441</v>
+      </c>
+      <c r="G85" s="19"/>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A86" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="B86" s="19" t="s">
+        <v>443</v>
+      </c>
+      <c r="C86" s="19" t="s">
+        <v>443</v>
+      </c>
+      <c r="D86" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E86" s="20">
+        <v>133</v>
+      </c>
+      <c r="F86" s="19" t="s">
+        <v>444</v>
+      </c>
+      <c r="G86" s="23" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A87" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="B87" s="19" t="s">
+        <v>235</v>
+      </c>
+      <c r="C87" s="19" t="s">
+        <v>235</v>
+      </c>
+      <c r="D87" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E87" s="20">
+        <v>41</v>
+      </c>
+      <c r="F87" s="19" t="s">
+        <v>371</v>
+      </c>
+      <c r="G87" s="19"/>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A88" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="B88" s="19" t="s">
+        <v>398</v>
+      </c>
+      <c r="C88" s="19" t="s">
+        <v>398</v>
+      </c>
+      <c r="D88" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E88" s="20">
+        <v>11</v>
+      </c>
+      <c r="F88" s="19" t="s">
+        <v>371</v>
+      </c>
+      <c r="G88" s="19"/>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A89" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="B89" s="19" t="s">
+        <v>399</v>
+      </c>
+      <c r="C89" s="19" t="s">
+        <v>399</v>
+      </c>
+      <c r="D89" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E89" s="20">
+        <v>68</v>
+      </c>
+      <c r="F89" s="19" t="s">
+        <v>371</v>
+      </c>
+      <c r="G89" s="19"/>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A90" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="B90" s="19" t="s">
+        <v>400</v>
+      </c>
+      <c r="C90" s="19" t="s">
+        <v>400</v>
+      </c>
+      <c r="D90" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E90" s="20">
+        <v>2</v>
+      </c>
+      <c r="F90" s="19" t="s">
+        <v>371</v>
+      </c>
+      <c r="G90" s="19"/>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A91" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="B91" s="19" t="s">
+        <v>239</v>
+      </c>
+      <c r="C91" s="19" t="s">
+        <v>239</v>
+      </c>
+      <c r="D91" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E91" s="20">
+        <v>48</v>
+      </c>
+      <c r="F91" s="19" t="s">
+        <v>441</v>
+      </c>
+      <c r="G91" s="19"/>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A92" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="B92" s="19" t="s">
+        <v>246</v>
+      </c>
+      <c r="C92" s="19" t="s">
+        <v>246</v>
+      </c>
+      <c r="D92" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E92" s="20">
+        <v>58</v>
+      </c>
+      <c r="F92" s="19" t="s">
+        <v>441</v>
+      </c>
+      <c r="G92" s="19"/>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A93" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="B93" s="19" t="s">
+        <v>446</v>
+      </c>
+      <c r="C93" s="19" t="s">
+        <v>446</v>
+      </c>
+      <c r="D93" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E93" s="20">
+        <v>551</v>
+      </c>
+      <c r="F93" s="19" t="s">
+        <v>447</v>
+      </c>
+      <c r="G93" s="19"/>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A94" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="B94" s="19" t="s">
+        <v>448</v>
+      </c>
+      <c r="C94" s="19" t="s">
+        <v>448</v>
+      </c>
+      <c r="D94" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E94" s="20">
+        <v>437</v>
+      </c>
+      <c r="F94" s="19" t="s">
+        <v>449</v>
+      </c>
+      <c r="G94" s="19"/>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A95" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="B95" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="C95" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="D95" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E95" s="20">
+        <v>76</v>
+      </c>
+      <c r="F95" s="19" t="s">
+        <v>441</v>
+      </c>
+      <c r="G95" s="19"/>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A96" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="B96" s="19" t="s">
+        <v>256</v>
+      </c>
+      <c r="C96" s="19" t="s">
+        <v>256</v>
+      </c>
+      <c r="D96" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E96" s="20">
+        <v>17</v>
+      </c>
+      <c r="F96" s="19" t="s">
+        <v>441</v>
+      </c>
+      <c r="G96" s="19"/>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A97" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="B97" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="C97" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="D97" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E97" s="20">
+        <v>42</v>
+      </c>
+      <c r="F97" s="19" t="s">
+        <v>441</v>
+      </c>
+      <c r="G97" s="19"/>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A98" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="B98" s="19" t="s">
+        <v>267</v>
+      </c>
+      <c r="C98" s="19" t="s">
+        <v>267</v>
+      </c>
+      <c r="D98" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E98" s="20">
+        <v>0</v>
+      </c>
+      <c r="F98" s="19"/>
+      <c r="G98" s="19"/>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A99" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="B99" s="19" t="s">
+        <v>271</v>
+      </c>
+      <c r="C99" s="19" t="s">
+        <v>271</v>
+      </c>
+      <c r="D99" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E99" s="20">
+        <v>0</v>
+      </c>
+      <c r="F99" s="19"/>
+      <c r="G99" s="19"/>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A100" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="B100" s="19" t="s">
+        <v>279</v>
+      </c>
+      <c r="C100" s="19" t="s">
+        <v>279</v>
+      </c>
+      <c r="D100" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E100" s="20">
+        <v>199</v>
+      </c>
+      <c r="F100" s="19" t="s">
+        <v>450</v>
+      </c>
+      <c r="G100" s="23" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A101" s="20" t="s">
+        <v>451</v>
+      </c>
+      <c r="B101" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="C101" s="19"/>
+      <c r="D101" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E101" s="20">
+        <v>1</v>
+      </c>
+      <c r="F101" s="19"/>
+      <c r="G101" s="19" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A102" s="20" t="s">
+        <v>451</v>
+      </c>
+      <c r="B102" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C102" s="19"/>
+      <c r="D102" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E102" s="20">
+        <v>25</v>
+      </c>
+      <c r="F102" s="19"/>
+      <c r="G102" s="19" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A103" s="20" t="s">
+        <v>451</v>
+      </c>
+      <c r="B103" s="19" t="s">
+        <v>413</v>
+      </c>
+      <c r="C103" s="19"/>
+      <c r="D103" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E103" s="20">
+        <v>46</v>
+      </c>
+      <c r="F103" s="19"/>
+      <c r="G103" s="19" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A104" s="20" t="s">
+        <v>451</v>
+      </c>
+      <c r="B104" s="19" t="s">
+        <v>370</v>
+      </c>
+      <c r="C104" s="19"/>
+      <c r="D104" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E104" s="20">
+        <v>227</v>
+      </c>
+      <c r="F104" s="19" t="s">
+        <v>371</v>
+      </c>
+      <c r="G104" s="19" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A105" s="20" t="s">
+        <v>451</v>
+      </c>
+      <c r="B105" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="C105" s="19"/>
+      <c r="D105" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E105" s="20">
+        <v>345</v>
+      </c>
+      <c r="F105" s="19"/>
+      <c r="G105" s="19" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A106" s="20" t="s">
+        <v>451</v>
+      </c>
+      <c r="B106" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="C106" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="D106" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="E106" s="20">
+        <v>487</v>
+      </c>
+      <c r="F106" s="19"/>
+      <c r="G106" s="19" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A107" s="20" t="s">
+        <v>451</v>
+      </c>
+      <c r="B107" s="19" t="s">
+        <v>379</v>
+      </c>
+      <c r="C107" s="19" t="s">
+        <v>380</v>
+      </c>
+      <c r="D107" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="E107" s="20">
+        <v>89</v>
+      </c>
+      <c r="F107" s="19"/>
+      <c r="G107" s="19" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A108" s="20" t="s">
+        <v>451</v>
+      </c>
+      <c r="B108" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="C108" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D108" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E108" s="20">
+        <v>30</v>
+      </c>
+      <c r="F108" s="19"/>
+      <c r="G108" s="19" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A109" s="20" t="s">
+        <v>451</v>
+      </c>
+      <c r="B109" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="C109" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="D109" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E109" s="20">
+        <v>112</v>
+      </c>
+      <c r="F109" s="19"/>
+      <c r="G109" s="19"/>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A110" s="20" t="s">
+        <v>451</v>
+      </c>
+      <c r="B110" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="C110" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="D110" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E110" s="20">
+        <v>56</v>
+      </c>
+      <c r="F110" s="19" t="s">
+        <v>371</v>
+      </c>
+      <c r="G110" s="19" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A111" s="20" t="s">
+        <v>451</v>
+      </c>
+      <c r="B111" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="C111" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="D111" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E111" s="20">
+        <v>93</v>
+      </c>
+      <c r="F111" s="19" t="s">
+        <v>371</v>
+      </c>
+      <c r="G111" s="19" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A112" s="20" t="s">
+        <v>451</v>
+      </c>
+      <c r="B112" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="C112" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="D112" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E112" s="20">
+        <v>92</v>
+      </c>
+      <c r="F112" s="19" t="s">
+        <v>371</v>
+      </c>
+      <c r="G112" s="19" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A113" s="20" t="s">
+        <v>451</v>
+      </c>
+      <c r="B113" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="C113" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="D113" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E113" s="20">
+        <v>92</v>
+      </c>
+      <c r="F113" s="19" t="s">
+        <v>371</v>
+      </c>
+      <c r="G113" s="19" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A114" s="20" t="s">
+        <v>451</v>
+      </c>
+      <c r="B114" s="19" t="s">
+        <v>392</v>
+      </c>
+      <c r="C114" s="19"/>
+      <c r="D114" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E114" s="20">
+        <v>181</v>
+      </c>
+      <c r="F114" s="19"/>
+      <c r="G114" s="19" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A115" s="20" t="s">
+        <v>451</v>
+      </c>
+      <c r="B115" s="19" t="s">
+        <v>239</v>
+      </c>
+      <c r="C115" s="19" t="s">
+        <v>239</v>
+      </c>
+      <c r="D115" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E115" s="20">
+        <v>57</v>
+      </c>
+      <c r="F115" s="19" t="s">
+        <v>371</v>
+      </c>
+      <c r="G115" s="19" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A116" s="20" t="s">
+        <v>451</v>
+      </c>
+      <c r="B116" s="19" t="s">
+        <v>242</v>
+      </c>
+      <c r="C116" s="19" t="s">
+        <v>242</v>
+      </c>
+      <c r="D116" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E116" s="20">
+        <v>124</v>
+      </c>
+      <c r="F116" s="19"/>
+      <c r="G116" s="19"/>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A117" s="20" t="s">
+        <v>451</v>
+      </c>
+      <c r="B117" s="19" t="s">
+        <v>453</v>
+      </c>
+      <c r="C117" s="19"/>
+      <c r="D117" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E117" s="20">
+        <v>219</v>
+      </c>
+      <c r="F117" s="19" t="s">
+        <v>371</v>
+      </c>
+      <c r="G117" s="19" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A118" s="20" t="s">
+        <v>451</v>
+      </c>
+      <c r="B118" s="19" t="s">
+        <v>454</v>
+      </c>
+      <c r="C118" s="19"/>
+      <c r="D118" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E118" s="20">
+        <v>3032</v>
+      </c>
+      <c r="F118" s="19" t="s">
+        <v>455</v>
+      </c>
+      <c r="G118" s="19" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A119" s="20" t="s">
+        <v>451</v>
+      </c>
+      <c r="B119" s="19" t="s">
+        <v>246</v>
+      </c>
+      <c r="C119" s="19" t="s">
+        <v>246</v>
+      </c>
+      <c r="D119" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E119" s="20">
+        <v>58</v>
+      </c>
+      <c r="F119" s="19" t="s">
+        <v>371</v>
+      </c>
+      <c r="G119" s="19" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A120" s="20" t="s">
+        <v>451</v>
+      </c>
+      <c r="B120" s="19" t="s">
+        <v>446</v>
+      </c>
+      <c r="C120" s="19" t="s">
+        <v>446</v>
+      </c>
+      <c r="D120" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E120" s="20">
+        <v>581</v>
+      </c>
+      <c r="F120" s="19" t="s">
+        <v>371</v>
+      </c>
+      <c r="G120" s="19" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A121" s="20" t="s">
+        <v>451</v>
+      </c>
+      <c r="B121" s="19" t="s">
+        <v>448</v>
+      </c>
+      <c r="C121" s="19" t="s">
+        <v>448</v>
+      </c>
+      <c r="D121" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E121" s="20">
+        <v>441</v>
+      </c>
+      <c r="F121" s="19" t="s">
+        <v>371</v>
+      </c>
+      <c r="G121" s="19" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A122" s="20" t="s">
+        <v>451</v>
+      </c>
+      <c r="B122" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="C122" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="D122" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E122" s="20">
+        <v>76</v>
+      </c>
+      <c r="F122" s="19"/>
+      <c r="G122" s="19" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A123" s="20" t="s">
+        <v>451</v>
+      </c>
+      <c r="B123" s="19" t="s">
+        <v>256</v>
+      </c>
+      <c r="C123" s="19" t="s">
+        <v>256</v>
+      </c>
+      <c r="D123" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E123" s="20">
+        <v>19</v>
+      </c>
+      <c r="F123" s="19"/>
+      <c r="G123" s="19" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A124" s="20" t="s">
+        <v>451</v>
+      </c>
+      <c r="B124" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="C124" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="D124" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E124" s="20">
+        <v>42</v>
+      </c>
+      <c r="F124" s="19"/>
+      <c r="G124" s="19" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A125" s="20" t="s">
+        <v>451</v>
+      </c>
+      <c r="B125" s="19" t="s">
+        <v>267</v>
+      </c>
+      <c r="C125" s="19" t="s">
+        <v>267</v>
+      </c>
+      <c r="D125" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E125" s="20">
+        <v>24</v>
+      </c>
+      <c r="F125" s="19"/>
+      <c r="G125" s="19" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A126" s="20" t="s">
+        <v>451</v>
+      </c>
+      <c r="B126" s="19" t="s">
+        <v>271</v>
+      </c>
+      <c r="C126" s="19" t="s">
+        <v>271</v>
+      </c>
+      <c r="D126" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E126" s="20">
+        <v>14</v>
+      </c>
+      <c r="F126" s="19" t="s">
+        <v>456</v>
+      </c>
+      <c r="G126" s="19" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A127" s="20" t="s">
+        <v>451</v>
+      </c>
+      <c r="B127" s="19" t="s">
+        <v>279</v>
+      </c>
+      <c r="C127" s="19" t="s">
+        <v>279</v>
+      </c>
+      <c r="D127" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="E127" s="20">
+        <v>200</v>
+      </c>
+      <c r="F127" s="19" t="s">
+        <v>457</v>
+      </c>
+      <c r="G127" s="23" t="s">
+        <v>458</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G127" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="4" width="34" customWidth="1"/>
+    <col min="5" max="5" width="40" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>459</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>460</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>461</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>462</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>463</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>465</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>466</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>466</v>
+      </c>
+      <c r="E3" s="23" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="20" t="s">
+        <v>374</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>468</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>465</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>465</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="25.5" x14ac:dyDescent="0.3">
+      <c r="A5" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>470</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>470</v>
+      </c>
+      <c r="E5" s="23" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>472</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>470</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>472</v>
+      </c>
+      <c r="E6" s="19"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>473</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>472</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>473</v>
+      </c>
+      <c r="E7" s="19"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="20" t="s">
+        <v>391</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>468</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>473</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>468</v>
+      </c>
+      <c r="E8" s="19"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="20" t="s">
+        <v>279</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>280</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>280</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>287</v>
+      </c>
+      <c r="E9" s="23" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="20" t="s">
+        <v>286</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>287</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>287</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>475</v>
+      </c>
+      <c r="E10" s="23" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="25.5" x14ac:dyDescent="0.3">
+      <c r="A11" s="20" t="s">
+        <v>477</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>478</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>479</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>480</v>
+      </c>
+      <c r="E11" s="23" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="25" t="s">
+        <v>482</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>